--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -574,7 +574,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -584,12 +584,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -639,17 +633,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="102">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -199,7 +205,103 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTERED</t>
+    <t>DIESEL DOUBLE FILTER</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>10:21</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>14:21</t>
+  </si>
+  <si>
+    <t>10:28</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>17:27</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>11:24</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>10:54</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>15:44</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>17:41</t>
+  </si>
+  <si>
+    <t>08:17</t>
+  </si>
+  <si>
+    <t>13:59</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 1</t>
@@ -617,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -630,10 +732,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -667,22 +771,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2">
         <v>22.35</v>
@@ -699,25 +809,31 @@
       <c r="J2">
         <v>35.09</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>111612</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3">
         <v>142</v>
@@ -734,25 +850,31 @@
       <c r="J3">
         <v>239.98</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>111620</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4">
         <v>21.46</v>
@@ -769,25 +891,31 @@
       <c r="J4">
         <v>33.69</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>190756</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5">
         <v>60</v>
@@ -804,25 +932,31 @@
       <c r="J5">
         <v>101.4</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>111761</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <v>47.01</v>
@@ -839,25 +973,31 @@
       <c r="J6">
         <v>79.45</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>191331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>25.07</v>
@@ -874,25 +1014,31 @@
       <c r="J7">
         <v>18.8</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>191394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8">
         <v>44.42</v>
@@ -909,25 +1055,31 @@
       <c r="J8">
         <v>69.73999999999999</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>191526</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9">
         <v>30</v>
@@ -944,25 +1096,31 @@
       <c r="J9">
         <v>47.1</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>192417</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F10">
         <v>44.26</v>
@@ -979,25 +1137,31 @@
       <c r="J10">
         <v>73.47</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>193009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F11">
         <v>31.04</v>
@@ -1014,25 +1178,31 @@
       <c r="J11">
         <v>48.73</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>112236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F12">
         <v>53.64</v>
@@ -1049,25 +1219,31 @@
       <c r="J12">
         <v>89.04000000000001</v>
       </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>112447</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F13">
         <v>107.87</v>
@@ -1084,25 +1260,31 @@
       <c r="J13">
         <v>179.06</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>112486</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F14">
         <v>22</v>
@@ -1119,25 +1301,31 @@
       <c r="J14">
         <v>34.54</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>112494</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F15">
         <v>25</v>
@@ -1154,25 +1342,31 @@
       <c r="J15">
         <v>39.25</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" t="s">
+        <v>77</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>193468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F16">
         <v>163.99</v>
@@ -1189,34 +1383,40 @@
       <c r="J16">
         <v>272.22</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="K16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>112509</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F17">
         <v>67.18000000000001</v>
       </c>
       <c r="G17" s="1">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H17">
-        <v>126.3</v>
+        <v>128.31</v>
       </c>
       <c r="I17" s="1">
         <v>1.91</v>
@@ -1224,25 +1424,31 @@
       <c r="J17">
         <v>128.31</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="K17" t="s">
+        <v>79</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>193484</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F18">
         <v>31.4</v>
@@ -1259,25 +1465,31 @@
       <c r="J18">
         <v>51.5</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="s">
+        <v>80</v>
+      </c>
+      <c r="L18">
         <v>429467</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="M18">
+        <v>194677</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F19">
         <v>68.09999999999999</v>
@@ -1294,25 +1506,31 @@
       <c r="J19">
         <v>111.68</v>
       </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="K19" t="s">
+        <v>81</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>195056</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F20">
         <v>28.44</v>
@@ -1329,25 +1547,31 @@
       <c r="J20">
         <v>20.48</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="K20" t="s">
+        <v>82</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>195308</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F21">
         <v>30.02</v>
@@ -1364,25 +1588,31 @@
       <c r="J21">
         <v>46.83</v>
       </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="K21" t="s">
+        <v>83</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>109957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F22">
         <v>21.6</v>
@@ -1399,25 +1629,31 @@
       <c r="J22">
         <v>33.7</v>
       </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="K22" t="s">
+        <v>84</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>195815</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F23">
         <v>35.22</v>
@@ -1434,25 +1670,31 @@
       <c r="J23">
         <v>54.94</v>
       </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="K23" t="s">
+        <v>85</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>195913</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F24">
         <v>47.82</v>
@@ -1469,25 +1711,31 @@
       <c r="J24">
         <v>74.59999999999999</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="K24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>196868</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F25">
         <v>59.67</v>
@@ -1504,25 +1752,31 @@
       <c r="J25">
         <v>96.67</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="K25" t="s">
+        <v>87</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>113857</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F26">
         <v>40.05</v>
@@ -1539,34 +1793,40 @@
       <c r="J26">
         <v>64.88</v>
       </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="K26" t="s">
+        <v>88</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>197384</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F27">
         <v>65.53</v>
       </c>
       <c r="G27" s="1">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H27">
-        <v>120.58</v>
+        <v>122.54</v>
       </c>
       <c r="I27" s="1">
         <v>1.87</v>
@@ -1574,25 +1834,31 @@
       <c r="J27">
         <v>122.54</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="K27" t="s">
+        <v>89</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>113960</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F28">
         <v>23.29</v>
@@ -1609,25 +1875,31 @@
       <c r="J28">
         <v>36.33</v>
       </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="K28" t="s">
+        <v>90</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>114200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F29">
         <v>172</v>
@@ -1644,25 +1916,31 @@
       <c r="J29">
         <v>276.92</v>
       </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="K29" t="s">
+        <v>91</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>198049</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F30">
         <v>138.96</v>
@@ -1679,25 +1957,31 @@
       <c r="J30">
         <v>223.73</v>
       </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="K30" t="s">
+        <v>92</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>114217</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F31">
         <v>28.21</v>
@@ -1714,25 +1998,31 @@
       <c r="J31">
         <v>19.18</v>
       </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="K31" t="s">
+        <v>93</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>198230</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F32">
         <v>37.44</v>
@@ -1749,25 +2039,31 @@
       <c r="J32">
         <v>58.41</v>
       </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="K32" t="s">
+        <v>94</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>199460</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F33">
         <v>33.75</v>
@@ -1784,13 +2080,19 @@
       <c r="J33">
         <v>52.65</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="K33" t="s">
+        <v>95</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>219395</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="3" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1798,18 +2100,18 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:13">
       <c r="A37" s="4" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>7</v>
@@ -1818,9 +2120,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:13">
       <c r="A38" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B38" s="6">
         <v>1128.95</v>
@@ -1838,9 +2140,9 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:13">
       <c r="A39" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B39" s="6">
         <v>425.41</v>
@@ -1858,9 +2160,9 @@
         <v>665.6</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:13">
       <c r="A40" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B40" s="6">
         <v>132.71</v>
@@ -1869,18 +2171,18 @@
         <v>2</v>
       </c>
       <c r="D40" s="7">
-        <v>1.8603</v>
+        <v>1.8902</v>
       </c>
       <c r="E40" s="6">
-        <v>246.88</v>
+        <v>250.85</v>
       </c>
       <c r="F40" s="6">
         <v>250.85</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:13">
       <c r="A41" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B41" s="6">
         <v>81.72</v>
@@ -1898,9 +2200,9 @@
         <v>58.46</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:13">
       <c r="A42" s="8" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="B42" s="9">
         <v>1768.79</v>
@@ -1910,7 +2212,7 @@
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="9">
-        <v>2783.49</v>
+        <v>2787.46</v>
       </c>
       <c r="F42" s="9">
         <v>2834.91</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="137">
   <si>
     <t>Дата</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -91,6 +85,33 @@
     <t>2026-06-15</t>
   </si>
   <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
@@ -100,6 +121,12 @@
     <t>Варна Порт</t>
   </si>
   <si>
+    <t>София България</t>
+  </si>
+  <si>
+    <t>Търговище</t>
+  </si>
+  <si>
     <t>В5328РМ</t>
   </si>
   <si>
@@ -148,6 +175,12 @@
     <t>В5654ВН</t>
   </si>
   <si>
+    <t>В9933СМ</t>
+  </si>
+  <si>
+    <t>В6476ВС</t>
+  </si>
+  <si>
     <t>78970155027722259</t>
   </si>
   <si>
@@ -196,6 +229,12 @@
     <t>78970155027722309</t>
   </si>
   <si>
+    <t>78970155027722176</t>
+  </si>
+  <si>
+    <t>78970155027722283</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
@@ -205,103 +244,169 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>10:21</t>
-  </si>
-  <si>
-    <t>12:34</t>
-  </si>
-  <si>
-    <t>14:21</t>
-  </si>
-  <si>
-    <t>10:28</t>
-  </si>
-  <si>
-    <t>11:31</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>12:07</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>14:53</t>
-  </si>
-  <si>
-    <t>08:42</t>
-  </si>
-  <si>
-    <t>17:27</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>11:24</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>14:41</t>
-  </si>
-  <si>
-    <t>10:54</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>15:44</t>
-  </si>
-  <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>13:01</t>
-  </si>
-  <si>
-    <t>17:41</t>
-  </si>
-  <si>
-    <t>08:17</t>
-  </si>
-  <si>
-    <t>13:59</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>2026-06-01 10:14:20</t>
+  </si>
+  <si>
+    <t>2026-06-01 10:21:58</t>
+  </si>
+  <si>
+    <t>2026-06-01 12:34:32</t>
+  </si>
+  <si>
+    <t>2026-06-01 14:21:49</t>
+  </si>
+  <si>
+    <t>2026-06-02 10:28:40</t>
+  </si>
+  <si>
+    <t>2026-06-02 11:31:25</t>
+  </si>
+  <si>
+    <t>2026-06-02 13:38:35</t>
+  </si>
+  <si>
+    <t>2026-06-03 15:50:22</t>
+  </si>
+  <si>
+    <t>2026-06-04 14:35:45</t>
+  </si>
+  <si>
+    <t>2026-06-04 14:40:37</t>
+  </si>
+  <si>
+    <t>2026-06-05 10:00:43</t>
+  </si>
+  <si>
+    <t>2026-06-05 11:27:52</t>
+  </si>
+  <si>
+    <t>2026-06-05 11:35:28</t>
+  </si>
+  <si>
+    <t>2026-06-05 11:45:52</t>
+  </si>
+  <si>
+    <t>2026-06-05 12:07:55</t>
+  </si>
+  <si>
+    <t>2026-06-05 12:10:40</t>
+  </si>
+  <si>
+    <t>2026-06-07 14:53:19</t>
+  </si>
+  <si>
+    <t>2026-06-08 08:42:56</t>
+  </si>
+  <si>
+    <t>2026-06-08 17:27:37</t>
+  </si>
+  <si>
+    <t>2026-06-09 08:53:34</t>
+  </si>
+  <si>
+    <t>2026-06-09 11:24:33</t>
+  </si>
+  <si>
+    <t>2026-06-09 13:11:10</t>
+  </si>
+  <si>
+    <t>2026-06-10 14:41:52</t>
+  </si>
+  <si>
+    <t>2026-06-11 10:54:17</t>
+  </si>
+  <si>
+    <t>2026-06-11 11:04:16</t>
+  </si>
+  <si>
+    <t>2026-06-11 15:44:22</t>
+  </si>
+  <si>
+    <t>2026-06-12 12:13:27</t>
+  </si>
+  <si>
+    <t>2026-06-12 12:56:36</t>
+  </si>
+  <si>
+    <t>2026-06-12 13:01:11</t>
+  </si>
+  <si>
+    <t>2026-06-12 17:41:34</t>
+  </si>
+  <si>
+    <t>2026-06-15 08:17:05</t>
+  </si>
+  <si>
+    <t>2026-06-15 13:58:35</t>
+  </si>
+  <si>
+    <t>2026-06-16 11:21:15</t>
+  </si>
+  <si>
+    <t>2026-06-16 15:42:05</t>
+  </si>
+  <si>
+    <t>2026-06-17 10:38:52</t>
+  </si>
+  <si>
+    <t>2026-06-17 12:33:26</t>
+  </si>
+  <si>
+    <t>2026-06-17 16:36:10</t>
+  </si>
+  <si>
+    <t>2026-06-17 17:10:57</t>
+  </si>
+  <si>
+    <t>2026-06-17 18:51:09</t>
+  </si>
+  <si>
+    <t>2026-06-18 09:46:41</t>
+  </si>
+  <si>
+    <t>2026-06-18 14:27:50</t>
+  </si>
+  <si>
+    <t>2026-06-19 08:49:25</t>
+  </si>
+  <si>
+    <t>2026-06-19 12:30:57</t>
+  </si>
+  <si>
+    <t>2026-06-20 17:32:32</t>
+  </si>
+  <si>
+    <t>2026-06-22 11:42:32</t>
+  </si>
+  <si>
+    <t>2026-06-22 13:10:57</t>
+  </si>
+  <si>
+    <t>2026-06-23 12:49:20</t>
+  </si>
+  <si>
+    <t>2026-06-23 13:24:59</t>
+  </si>
+  <si>
+    <t>2026-06-23 14:18:28</t>
+  </si>
+  <si>
+    <t>2026-06-23 16:05:51</t>
+  </si>
+  <si>
+    <t>2026-06-24 12:26:42</t>
+  </si>
+  <si>
+    <t>2026-06-24 17:17:13</t>
+  </si>
+  <si>
+    <t>2026-06-25 08:38:08</t>
+  </si>
+  <si>
+    <t>2026-06-25 09:32:07</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 1</t>
@@ -719,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -732,12 +837,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -771,28 +874,22 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F2">
         <v>22.35</v>
@@ -810,30 +907,24 @@
         <v>35.09</v>
       </c>
       <c r="K2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>111612</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F3">
         <v>142</v>
@@ -851,30 +942,24 @@
         <v>239.98</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>111620</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F4">
         <v>21.46</v>
@@ -892,30 +977,24 @@
         <v>33.69</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>190756</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <v>60</v>
@@ -933,30 +1012,24 @@
         <v>101.4</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>111761</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F6">
         <v>47.01</v>
@@ -974,30 +1047,24 @@
         <v>79.45</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>191331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>25.07</v>
@@ -1015,30 +1082,24 @@
         <v>18.8</v>
       </c>
       <c r="K7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>191394</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F8">
         <v>44.42</v>
@@ -1056,30 +1117,24 @@
         <v>69.73999999999999</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>191526</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F9">
         <v>30</v>
@@ -1097,30 +1152,24 @@
         <v>47.1</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>192417</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F10">
         <v>44.26</v>
@@ -1138,30 +1187,24 @@
         <v>73.47</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>193009</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F11">
         <v>31.04</v>
@@ -1179,30 +1222,24 @@
         <v>48.73</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>112236</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F12">
         <v>53.64</v>
@@ -1220,30 +1257,24 @@
         <v>89.04000000000001</v>
       </c>
       <c r="K12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
         <v>74</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>112447</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>61</v>
       </c>
       <c r="F13">
         <v>107.87</v>
@@ -1261,30 +1292,24 @@
         <v>179.06</v>
       </c>
       <c r="K13" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>112486</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F14">
         <v>22</v>
@@ -1302,30 +1327,24 @@
         <v>34.54</v>
       </c>
       <c r="K14" t="s">
-        <v>76</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>112494</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F15">
         <v>25</v>
@@ -1343,30 +1362,24 @@
         <v>39.25</v>
       </c>
       <c r="K15" t="s">
-        <v>77</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>193468</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F16">
         <v>163.99</v>
@@ -1384,39 +1397,33 @@
         <v>272.22</v>
       </c>
       <c r="K16" t="s">
-        <v>78</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>112509</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F17">
         <v>67.18000000000001</v>
       </c>
       <c r="G17" s="1">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H17">
-        <v>128.31</v>
+        <v>126.3</v>
       </c>
       <c r="I17" s="1">
         <v>1.91</v>
@@ -1425,30 +1432,24 @@
         <v>128.31</v>
       </c>
       <c r="K17" t="s">
-        <v>79</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>193484</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F18">
         <v>31.4</v>
@@ -1466,30 +1467,24 @@
         <v>51.5</v>
       </c>
       <c r="K18" t="s">
-        <v>80</v>
-      </c>
-      <c r="L18">
-        <v>429467</v>
-      </c>
-      <c r="M18">
-        <v>194677</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F19">
         <v>68.09999999999999</v>
@@ -1507,30 +1502,24 @@
         <v>111.68</v>
       </c>
       <c r="K19" t="s">
-        <v>81</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>195056</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F20">
         <v>28.44</v>
@@ -1548,30 +1537,24 @@
         <v>20.48</v>
       </c>
       <c r="K20" t="s">
-        <v>82</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>195308</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F21">
         <v>30.02</v>
@@ -1589,30 +1572,24 @@
         <v>46.83</v>
       </c>
       <c r="K21" t="s">
-        <v>83</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>109957</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F22">
         <v>21.6</v>
@@ -1630,30 +1607,24 @@
         <v>33.7</v>
       </c>
       <c r="K22" t="s">
-        <v>84</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>195815</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F23">
         <v>35.22</v>
@@ -1671,30 +1642,24 @@
         <v>54.94</v>
       </c>
       <c r="K23" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>195913</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F24">
         <v>47.82</v>
@@ -1712,30 +1677,24 @@
         <v>74.59999999999999</v>
       </c>
       <c r="K24" t="s">
-        <v>86</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>196868</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F25">
         <v>59.67</v>
@@ -1753,30 +1712,24 @@
         <v>96.67</v>
       </c>
       <c r="K25" t="s">
-        <v>87</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>113857</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F26">
         <v>40.05</v>
@@ -1794,39 +1747,33 @@
         <v>64.88</v>
       </c>
       <c r="K26" t="s">
-        <v>88</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>197384</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="F27">
         <v>65.53</v>
       </c>
       <c r="G27" s="1">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="H27">
-        <v>122.54</v>
+        <v>120.58</v>
       </c>
       <c r="I27" s="1">
         <v>1.87</v>
@@ -1835,30 +1782,24 @@
         <v>122.54</v>
       </c>
       <c r="K27" t="s">
-        <v>89</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>113960</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F28">
         <v>23.29</v>
@@ -1876,30 +1817,24 @@
         <v>36.33</v>
       </c>
       <c r="K28" t="s">
-        <v>90</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>114200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F29">
         <v>172</v>
@@ -1917,30 +1852,24 @@
         <v>276.92</v>
       </c>
       <c r="K29" t="s">
-        <v>91</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>198049</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F30">
         <v>138.96</v>
@@ -1958,30 +1887,24 @@
         <v>223.73</v>
       </c>
       <c r="K30" t="s">
-        <v>92</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>114217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F31">
         <v>28.21</v>
@@ -1999,30 +1922,24 @@
         <v>19.18</v>
       </c>
       <c r="K31" t="s">
-        <v>93</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>198230</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F32">
         <v>37.44</v>
@@ -2040,30 +1957,24 @@
         <v>58.41</v>
       </c>
       <c r="K32" t="s">
-        <v>94</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>199460</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F33">
         <v>33.75</v>
@@ -2081,146 +1992,910 @@
         <v>52.65</v>
       </c>
       <c r="K33" t="s">
-        <v>95</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>219395</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E37" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34">
+        <v>35.54</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="H34">
+        <v>55.44</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="J34">
+        <v>56.51</v>
+      </c>
+      <c r="K34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35">
+        <v>67.17</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="H35">
+        <v>122.25</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="J35">
+        <v>124.26</v>
+      </c>
+      <c r="K35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36">
+        <v>42.77</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H36">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J36">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="K36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37">
+        <v>70.38</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="H37">
+        <v>109.79</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="J37">
+        <v>111.9</v>
+      </c>
+      <c r="K37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38">
+        <v>29</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H38">
+        <v>44.08</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J38">
+        <v>44.95</v>
+      </c>
+      <c r="K38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39">
+        <v>25.31</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H39">
+        <v>16.7</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J39">
+        <v>16.96</v>
+      </c>
+      <c r="K39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40">
+        <v>51.72</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="H40">
+        <v>95.16</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1.87</v>
+      </c>
+      <c r="J40">
+        <v>96.72</v>
+      </c>
+      <c r="K40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41">
+        <v>38.05</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="H41">
+        <v>58.98</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="J41">
+        <v>60.12</v>
+      </c>
+      <c r="K41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42">
+        <v>32.31</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H42">
+        <v>49.11</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J42">
+        <v>50.08</v>
+      </c>
+      <c r="K42" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43">
+        <v>48.06</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H43">
+        <v>73.53</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J43">
+        <v>74.97</v>
+      </c>
+      <c r="K43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44">
+        <v>122.01</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H44">
+        <v>186.68</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J44">
+        <v>190.34</v>
+      </c>
+      <c r="K44" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45">
+        <v>50</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="H45">
+        <v>88.5</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="J45">
+        <v>90</v>
+      </c>
+      <c r="K45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46">
+        <v>41.19</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H46">
+        <v>61.37</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J46">
+        <v>62.61</v>
+      </c>
+      <c r="K46" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47">
+        <v>115.63</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H47">
+        <v>172.29</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J47">
+        <v>175.76</v>
+      </c>
+      <c r="K47" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48">
+        <v>28.29</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H48">
+        <v>41.87</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J48">
+        <v>42.72</v>
+      </c>
+      <c r="K48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49">
+        <v>42.06</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H49">
+        <v>62.25</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J49">
+        <v>63.51</v>
+      </c>
+      <c r="K49" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50">
+        <v>35</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H50">
+        <v>51.8</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J50">
+        <v>52.85</v>
+      </c>
+      <c r="K50" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51">
+        <v>56.9</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H51">
+        <v>84.78</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J51">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="K51" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52">
+        <v>138</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H52">
+        <v>204.24</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J52">
+        <v>208.38</v>
+      </c>
+      <c r="K52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53">
+        <v>31.91</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H53">
+        <v>20.74</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J53">
+        <v>21.06</v>
+      </c>
+      <c r="K53" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54">
+        <v>59.57</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="H54">
+        <v>103.65</v>
+      </c>
+      <c r="I54" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="J54">
+        <v>105.44</v>
+      </c>
+      <c r="K54" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" t="s">
+        <v>73</v>
+      </c>
+      <c r="F55">
+        <v>28.16</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H55">
+        <v>41.68</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J55">
+        <v>42.52</v>
+      </c>
+      <c r="K55" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F59" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="6">
-        <v>1128.95</v>
-      </c>
-      <c r="C38" s="6">
-        <v>13</v>
-      </c>
-      <c r="D38" s="7">
-        <v>1.6175</v>
-      </c>
-      <c r="E38" s="6">
-        <v>1826.13</v>
-      </c>
-      <c r="F38" s="6">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="6">
-        <v>425.41</v>
-      </c>
-      <c r="C39" s="6">
-        <v>14</v>
-      </c>
-      <c r="D39" s="7">
-        <v>1.5346</v>
-      </c>
-      <c r="E39" s="6">
-        <v>652.84</v>
-      </c>
-      <c r="F39" s="6">
-        <v>665.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="6">
-        <v>132.71</v>
-      </c>
-      <c r="C40" s="6">
-        <v>2</v>
-      </c>
-      <c r="D40" s="7">
-        <v>1.8902</v>
-      </c>
-      <c r="E40" s="6">
-        <v>250.85</v>
-      </c>
-      <c r="F40" s="6">
-        <v>250.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B41" s="6">
-        <v>81.72</v>
-      </c>
-      <c r="C41" s="6">
-        <v>3</v>
-      </c>
-      <c r="D41" s="7">
-        <v>0.7053</v>
-      </c>
-      <c r="E41" s="6">
-        <v>57.64</v>
-      </c>
-      <c r="F41" s="6">
-        <v>58.46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B42" s="9">
-        <v>1768.79</v>
-      </c>
-      <c r="C42" s="9">
-        <v>32</v>
-      </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="9">
-        <v>2787.46</v>
-      </c>
-      <c r="F42" s="9">
-        <v>2834.91</v>
+    <row r="60" spans="1:11">
+      <c r="A60" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="6">
+        <v>1794.71</v>
+      </c>
+      <c r="C60" s="6">
+        <v>22</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1.5787</v>
+      </c>
+      <c r="E60" s="6">
+        <v>2833.23</v>
+      </c>
+      <c r="F60" s="6">
+        <v>2887.08</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6">
+        <v>663</v>
+      </c>
+      <c r="C61" s="6">
+        <v>21</v>
+      </c>
+      <c r="D61" s="7">
+        <v>1.5213</v>
+      </c>
+      <c r="E61" s="6">
+        <v>1008.64</v>
+      </c>
+      <c r="F61" s="6">
+        <v>1028.52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="6">
+        <v>361.17</v>
+      </c>
+      <c r="C62" s="6">
+        <v>6</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1.8175</v>
+      </c>
+      <c r="E62" s="6">
+        <v>656.4400000000001</v>
+      </c>
+      <c r="F62" s="6">
+        <v>667.27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="6">
+        <v>138.94</v>
+      </c>
+      <c r="C63" s="6">
+        <v>5</v>
+      </c>
+      <c r="D63" s="7">
+        <v>0.6843</v>
+      </c>
+      <c r="E63" s="6">
+        <v>95.08</v>
+      </c>
+      <c r="F63" s="6">
+        <v>96.48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" s="9">
+        <v>2957.82</v>
+      </c>
+      <c r="C64" s="9">
+        <v>54</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="9">
+        <v>4593.39</v>
+      </c>
+      <c r="F64" s="9">
+        <v>4679.35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A58:F58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="213">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -112,33 +121,42 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>София България</t>
-  </si>
-  <si>
-    <t>Търговище</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1160 София бул. България</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>В4239ВТ</t>
+  </si>
+  <si>
+    <t>В7341ВС</t>
+  </si>
+  <si>
+    <t>В2278РВ</t>
   </si>
   <si>
     <t>В5328РМ</t>
   </si>
   <si>
-    <t>В7341ВС</t>
-  </si>
-  <si>
-    <t>В2278РВ</t>
-  </si>
-  <si>
-    <t>В4239ВТ</t>
-  </si>
-  <si>
     <t>В6196РС</t>
   </si>
   <si>
@@ -181,18 +199,18 @@
     <t>В6476ВС</t>
   </si>
   <si>
+    <t>78970155027722325</t>
+  </si>
+  <si>
+    <t>78970155027722390</t>
+  </si>
+  <si>
+    <t>78970155027722226</t>
+  </si>
+  <si>
     <t>78970155027722259</t>
   </si>
   <si>
-    <t>78970155027722390</t>
-  </si>
-  <si>
-    <t>78970155027722226</t>
-  </si>
-  <si>
-    <t>78970155027722325</t>
-  </si>
-  <si>
     <t>78970155027722424</t>
   </si>
   <si>
@@ -235,178 +253,388 @@
     <t>78970155027722283</t>
   </si>
   <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>2026-06-01 10:14:20</t>
-  </si>
-  <si>
-    <t>2026-06-01 10:21:58</t>
-  </si>
-  <si>
-    <t>2026-06-01 12:34:32</t>
-  </si>
-  <si>
-    <t>2026-06-01 14:21:49</t>
-  </si>
-  <si>
-    <t>2026-06-02 10:28:40</t>
-  </si>
-  <si>
-    <t>2026-06-02 11:31:25</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:38:35</t>
-  </si>
-  <si>
-    <t>2026-06-03 15:50:22</t>
-  </si>
-  <si>
-    <t>2026-06-04 14:35:45</t>
-  </si>
-  <si>
-    <t>2026-06-04 14:40:37</t>
-  </si>
-  <si>
-    <t>2026-06-05 10:00:43</t>
-  </si>
-  <si>
-    <t>2026-06-05 11:27:52</t>
-  </si>
-  <si>
-    <t>2026-06-05 11:35:28</t>
-  </si>
-  <si>
-    <t>2026-06-05 11:45:52</t>
-  </si>
-  <si>
-    <t>2026-06-05 12:07:55</t>
-  </si>
-  <si>
-    <t>2026-06-05 12:10:40</t>
-  </si>
-  <si>
-    <t>2026-06-07 14:53:19</t>
-  </si>
-  <si>
-    <t>2026-06-08 08:42:56</t>
-  </si>
-  <si>
-    <t>2026-06-08 17:27:37</t>
-  </si>
-  <si>
-    <t>2026-06-09 08:53:34</t>
-  </si>
-  <si>
-    <t>2026-06-09 11:24:33</t>
-  </si>
-  <si>
-    <t>2026-06-09 13:11:10</t>
-  </si>
-  <si>
-    <t>2026-06-10 14:41:52</t>
-  </si>
-  <si>
-    <t>2026-06-11 10:54:17</t>
-  </si>
-  <si>
-    <t>2026-06-11 11:04:16</t>
-  </si>
-  <si>
-    <t>2026-06-11 15:44:22</t>
-  </si>
-  <si>
-    <t>2026-06-12 12:13:27</t>
-  </si>
-  <si>
-    <t>2026-06-12 12:56:36</t>
-  </si>
-  <si>
-    <t>2026-06-12 13:01:11</t>
-  </si>
-  <si>
-    <t>2026-06-12 17:41:34</t>
-  </si>
-  <si>
-    <t>2026-06-15 08:17:05</t>
-  </si>
-  <si>
-    <t>2026-06-15 13:58:35</t>
-  </si>
-  <si>
-    <t>2026-06-16 11:21:15</t>
-  </si>
-  <si>
-    <t>2026-06-16 15:42:05</t>
-  </si>
-  <si>
-    <t>2026-06-17 10:38:52</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:33:26</t>
-  </si>
-  <si>
-    <t>2026-06-17 16:36:10</t>
-  </si>
-  <si>
-    <t>2026-06-17 17:10:57</t>
-  </si>
-  <si>
-    <t>2026-06-17 18:51:09</t>
-  </si>
-  <si>
-    <t>2026-06-18 09:46:41</t>
-  </si>
-  <si>
-    <t>2026-06-18 14:27:50</t>
-  </si>
-  <si>
-    <t>2026-06-19 08:49:25</t>
-  </si>
-  <si>
-    <t>2026-06-19 12:30:57</t>
-  </si>
-  <si>
-    <t>2026-06-20 17:32:32</t>
-  </si>
-  <si>
-    <t>2026-06-22 11:42:32</t>
-  </si>
-  <si>
-    <t>2026-06-22 13:10:57</t>
-  </si>
-  <si>
-    <t>2026-06-23 12:49:20</t>
-  </si>
-  <si>
-    <t>2026-06-23 13:24:59</t>
-  </si>
-  <si>
-    <t>2026-06-23 14:18:28</t>
-  </si>
-  <si>
-    <t>2026-06-23 16:05:51</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:26:42</t>
-  </si>
-  <si>
-    <t>2026-06-24 17:17:13</t>
-  </si>
-  <si>
-    <t>2026-06-25 08:38:08</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:32:07</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:21:00</t>
+  </si>
+  <si>
+    <t>10:21:00</t>
+  </si>
+  <si>
+    <t>12:34:00</t>
+  </si>
+  <si>
+    <t>10:14:00</t>
+  </si>
+  <si>
+    <t>10:28:00</t>
+  </si>
+  <si>
+    <t>11:31:00</t>
+  </si>
+  <si>
+    <t>13:38:00</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>14:36:00</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>11:27:00</t>
+  </si>
+  <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
+    <t>11:45:00</t>
+  </si>
+  <si>
+    <t>12:10:00</t>
+  </si>
+  <si>
+    <t>12:07:00</t>
+  </si>
+  <si>
+    <t>14:53:00</t>
+  </si>
+  <si>
+    <t>08:43:00</t>
+  </si>
+  <si>
+    <t>17:27:00</t>
+  </si>
+  <si>
+    <t>11:24:00</t>
+  </si>
+  <si>
+    <t>13:11:00</t>
+  </si>
+  <si>
+    <t>08:53:00</t>
+  </si>
+  <si>
+    <t>14:42:00</t>
+  </si>
+  <si>
+    <t>11:04:00</t>
+  </si>
+  <si>
+    <t>10:54:00</t>
+  </si>
+  <si>
+    <t>15:44:00</t>
+  </si>
+  <si>
+    <t>12:56:00</t>
+  </si>
+  <si>
+    <t>12:13:00</t>
+  </si>
+  <si>
+    <t>13:01:00</t>
+  </si>
+  <si>
+    <t>17:41:00</t>
+  </si>
+  <si>
+    <t>08:17:00</t>
+  </si>
+  <si>
+    <t>13:58:00</t>
+  </si>
+  <si>
+    <t>11:21:00</t>
+  </si>
+  <si>
+    <t>15:42:00</t>
+  </si>
+  <si>
+    <t>10:38:00</t>
+  </si>
+  <si>
+    <t>12:33:00</t>
+  </si>
+  <si>
+    <t>17:10:00</t>
+  </si>
+  <si>
+    <t>16:36:00</t>
+  </si>
+  <si>
+    <t>18:51:00</t>
+  </si>
+  <si>
+    <t>09:46:00</t>
+  </si>
+  <si>
+    <t>14:28:00</t>
+  </si>
+  <si>
+    <t>08:49:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>17:32:00</t>
+  </si>
+  <si>
+    <t>11:42:00</t>
+  </si>
+  <si>
+    <t>14:18:00</t>
+  </si>
+  <si>
+    <t>12:49:00</t>
+  </si>
+  <si>
+    <t>13:24:00</t>
+  </si>
+  <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
+    <t>12:26:00</t>
+  </si>
+  <si>
+    <t>17:17:00</t>
+  </si>
+  <si>
+    <t>08:38:00</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>19:01:00</t>
+  </si>
+  <si>
+    <t>08:11:00</t>
+  </si>
+  <si>
+    <t>12:20:00</t>
+  </si>
+  <si>
+    <t>14:25:00</t>
+  </si>
+  <si>
+    <t>16:17:00</t>
+  </si>
+  <si>
+    <t>15:14:00</t>
+  </si>
+  <si>
+    <t>13:34:00</t>
+  </si>
+  <si>
+    <t>3232686248 3232686248</t>
+  </si>
+  <si>
+    <t>3232691761 3232691761</t>
+  </si>
+  <si>
+    <t>3232710782 3232710782</t>
+  </si>
+  <si>
+    <t>3232710881 3232710881</t>
+  </si>
+  <si>
+    <t>3232757525 3232757525</t>
+  </si>
+  <si>
+    <t>3232758035 3232758035</t>
+  </si>
+  <si>
+    <t>3232760556 3232760556</t>
+  </si>
+  <si>
+    <t>3232813815 3232813815</t>
+  </si>
+  <si>
+    <t>3232854070 3232854070</t>
+  </si>
+  <si>
+    <t>3232855289 3232855289</t>
+  </si>
+  <si>
+    <t>3232897290 3232897290</t>
+  </si>
+  <si>
+    <t>3232897633 3232897633</t>
+  </si>
+  <si>
+    <t>3232898447 3232898447</t>
+  </si>
+  <si>
+    <t>3232898660 3232898660</t>
+  </si>
+  <si>
+    <t>3232899237 3232899237</t>
+  </si>
+  <si>
+    <t>3232899819 3232899819</t>
+  </si>
+  <si>
+    <t>3233000955 3233000955</t>
+  </si>
+  <si>
+    <t>3233034665 3233034665</t>
+  </si>
+  <si>
+    <t>3233050060 3233050060</t>
+  </si>
+  <si>
+    <t>3233091924 3233091924</t>
+  </si>
+  <si>
+    <t>3233093740 3233093740</t>
+  </si>
+  <si>
+    <t>3233091990 3233091990</t>
+  </si>
+  <si>
+    <t>3233147844 3233147844</t>
+  </si>
+  <si>
+    <t>3233163453 3233163453</t>
+  </si>
+  <si>
+    <t>3233170821 3233170821</t>
+  </si>
+  <si>
+    <t>3233190056 3233190056</t>
+  </si>
+  <si>
+    <t>3233217094 3233217094</t>
+  </si>
+  <si>
+    <t>3233240095 3233240095</t>
+  </si>
+  <si>
+    <t>3233243235 3233243235</t>
+  </si>
+  <si>
+    <t>3233252069 3233252069</t>
+  </si>
+  <si>
+    <t>3233382813 3233382813</t>
+  </si>
+  <si>
+    <t>3233387555 3233387555</t>
+  </si>
+  <si>
+    <t>3233431938 3233431938</t>
+  </si>
+  <si>
+    <t>3233437288 3233437288</t>
+  </si>
+  <si>
+    <t>3233476268 3233476268</t>
+  </si>
+  <si>
+    <t>3233477745 3233477745</t>
+  </si>
+  <si>
+    <t>3233481374 3233481374</t>
+  </si>
+  <si>
+    <t>3233481688 3233481688</t>
+  </si>
+  <si>
+    <t>3233442278 3233442278</t>
+  </si>
+  <si>
+    <t>3233505285 3233505285</t>
+  </si>
+  <si>
+    <t>3233528464 3233528464</t>
+  </si>
+  <si>
+    <t>3233573922 3233573922</t>
+  </si>
+  <si>
+    <t>3233577118 3233577118</t>
+  </si>
+  <si>
+    <t>3233644967 3233644967</t>
+  </si>
+  <si>
+    <t>3233716816 3233716816</t>
+  </si>
+  <si>
+    <t>3233717825 3233717825</t>
+  </si>
+  <si>
+    <t>3233756382 3233756382</t>
+  </si>
+  <si>
+    <t>3233761553 3233761553</t>
+  </si>
+  <si>
+    <t>3233762105 3233762105</t>
+  </si>
+  <si>
+    <t>3233766938 3233766938</t>
+  </si>
+  <si>
+    <t>3233736453 3233736453</t>
+  </si>
+  <si>
+    <t>3233788829 3233788829</t>
+  </si>
+  <si>
+    <t>3233827289 3233827289</t>
+  </si>
+  <si>
+    <t>3233852310 3233852310</t>
+  </si>
+  <si>
+    <t>3233919596 3233919596</t>
+  </si>
+  <si>
+    <t>3233926271 3233926271</t>
+  </si>
+  <si>
+    <t>3234046600 3234046600</t>
+  </si>
+  <si>
+    <t>3234049452 3234049452</t>
+  </si>
+  <si>
+    <t>3234051393 3234051393</t>
+  </si>
+  <si>
+    <t>3234053822 3234053822</t>
+  </si>
+  <si>
+    <t>3234055108 3234055108</t>
+  </si>
+  <si>
+    <t>3234095088 3234095088</t>
+  </si>
+  <si>
+    <t>3234097119 3234097119</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 1</t>
@@ -824,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -833,14 +1061,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -874,2028 +1105,2919 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F2">
-        <v>22.35</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
+        <v>60</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
       </c>
       <c r="H2">
-        <v>34.42</v>
+        <v>1.66</v>
       </c>
       <c r="I2" s="1">
-        <v>1.57</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J2">
-        <v>35.09</v>
-      </c>
-      <c r="K2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>1.69</v>
+      </c>
+      <c r="K2" s="1">
+        <v>101.4</v>
+      </c>
+      <c r="L2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F3">
         <v>142</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>235.72</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.69</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>239.98</v>
       </c>
-      <c r="K3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F4">
         <v>21.46</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4">
         <v>1.54</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>33.05</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.57</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>33.69</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>86</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5">
+        <v>22.35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5">
+        <v>1.54</v>
+      </c>
+      <c r="I5" s="1">
+        <v>34.42</v>
+      </c>
+      <c r="J5">
+        <v>1.57</v>
+      </c>
+      <c r="K5" s="1">
+        <v>35.09</v>
+      </c>
+      <c r="L5" t="s">
+        <v>87</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5">
-        <v>60</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="H5">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J5">
-        <v>101.4</v>
-      </c>
-      <c r="K5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
       </c>
       <c r="F6">
         <v>47.01</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6">
         <v>1.66</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>78.04000000000001</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.69</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>79.45</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" t="s">
-        <v>75</v>
       </c>
       <c r="F7">
         <v>25.07</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7">
         <v>0.74</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>18.55</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>0.75</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>18.8</v>
       </c>
-      <c r="K7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>44.42</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8">
         <v>1.54</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>68.41</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.57</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>69.73999999999999</v>
       </c>
-      <c r="K8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F9">
         <v>30</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9">
         <v>1.54</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>46.2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.57</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>47.1</v>
       </c>
-      <c r="K9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>91</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F10">
         <v>44.26</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10">
         <v>1.63</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>72.14</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.66</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>73.47</v>
       </c>
-      <c r="K10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>92</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>31.04</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11">
         <v>1.54</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>47.8</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.57</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>48.73</v>
       </c>
-      <c r="K11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>93</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F12">
         <v>53.64</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12">
         <v>1.63</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>87.43000000000001</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.66</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>89.04000000000001</v>
       </c>
-      <c r="K12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>94</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F13">
         <v>107.87</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13">
         <v>1.63</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>175.83</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.66</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>179.06</v>
       </c>
-      <c r="K13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F14">
         <v>22</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14">
         <v>1.54</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>33.88</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.57</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>34.54</v>
       </c>
-      <c r="K14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F15">
         <v>25</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15">
         <v>1.54</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>38.5</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.57</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>39.25</v>
       </c>
-      <c r="K15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>97</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F16">
+        <v>67.18000000000001</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16">
+        <v>1.88</v>
+      </c>
+      <c r="I16" s="1">
+        <v>126.3</v>
+      </c>
+      <c r="J16">
+        <v>1.91</v>
+      </c>
+      <c r="K16" s="1">
+        <v>128.31</v>
+      </c>
+      <c r="L16" t="s">
+        <v>98</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17">
         <v>163.99</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17">
         <v>1.63</v>
       </c>
-      <c r="H16">
+      <c r="I17" s="1">
         <v>267.3</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J17">
         <v>1.66</v>
       </c>
-      <c r="J16">
+      <c r="K17" s="1">
         <v>272.22</v>
       </c>
-      <c r="K16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17">
-        <v>67.18000000000001</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1.88</v>
-      </c>
-      <c r="H17">
-        <v>126.3</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1.91</v>
-      </c>
-      <c r="J17">
-        <v>128.31</v>
-      </c>
-      <c r="K17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>99</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F18">
         <v>31.4</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18">
         <v>1.61</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>50.55</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.64</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>51.5</v>
       </c>
-      <c r="K18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>100</v>
+      </c>
+      <c r="M18">
+        <v>429467</v>
+      </c>
+      <c r="N18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F19">
         <v>68.09999999999999</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19">
         <v>1.61</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>109.64</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.64</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>111.68</v>
       </c>
-      <c r="K19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>101</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F20">
         <v>28.44</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20">
         <v>0.71</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="1">
         <v>20.19</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20">
         <v>0.72</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>20.48</v>
       </c>
-      <c r="K20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="s">
+        <v>102</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F21">
+        <v>21.6</v>
+      </c>
+      <c r="G21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21">
+        <v>1.53</v>
+      </c>
+      <c r="I21" s="1">
+        <v>33.05</v>
+      </c>
+      <c r="J21">
+        <v>1.56</v>
+      </c>
+      <c r="K21" s="1">
+        <v>33.7</v>
+      </c>
+      <c r="L21" t="s">
+        <v>103</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22">
+        <v>35.22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22">
+        <v>1.53</v>
+      </c>
+      <c r="I22" s="1">
+        <v>53.89</v>
+      </c>
+      <c r="J22">
+        <v>1.56</v>
+      </c>
+      <c r="K22" s="1">
+        <v>54.94</v>
+      </c>
+      <c r="L22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23">
         <v>30.02</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23">
         <v>1.53</v>
       </c>
-      <c r="H21">
+      <c r="I23" s="1">
         <v>45.93</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J23">
         <v>1.56</v>
       </c>
-      <c r="J21">
+      <c r="K23" s="1">
         <v>46.83</v>
       </c>
-      <c r="K21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22">
-        <v>21.6</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H22">
-        <v>33.05</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J22">
-        <v>33.7</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23">
-        <v>35.22</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H23">
-        <v>53.89</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J23">
-        <v>54.94</v>
-      </c>
-      <c r="K23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" t="s">
+        <v>105</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F24">
         <v>47.82</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24">
         <v>1.53</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="1">
         <v>73.16</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24">
         <v>1.56</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="1">
         <v>74.59999999999999</v>
       </c>
-      <c r="K24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24" t="s">
+        <v>106</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F25">
+        <v>40.05</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25">
+        <v>1.59</v>
+      </c>
+      <c r="I25" s="1">
+        <v>63.68</v>
+      </c>
+      <c r="J25">
+        <v>1.62</v>
+      </c>
+      <c r="K25" s="1">
+        <v>64.88</v>
+      </c>
+      <c r="L25" t="s">
+        <v>107</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26">
         <v>59.67</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26">
         <v>1.59</v>
       </c>
-      <c r="H25">
+      <c r="I26" s="1">
         <v>94.88</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J26">
         <v>1.62</v>
       </c>
-      <c r="J25">
+      <c r="K26" s="1">
         <v>96.67</v>
       </c>
-      <c r="K25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26">
-        <v>40.05</v>
-      </c>
-      <c r="G26" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="H26">
-        <v>63.68</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="J26">
-        <v>64.88</v>
-      </c>
-      <c r="K26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26" t="s">
+        <v>108</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F27">
         <v>65.53</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27">
         <v>1.84</v>
       </c>
-      <c r="H27">
+      <c r="I27" s="1">
         <v>120.58</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27">
         <v>1.87</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="1">
         <v>122.54</v>
       </c>
-      <c r="K27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27" t="s">
+        <v>109</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F28">
+        <v>172</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28">
+        <v>1.58</v>
+      </c>
+      <c r="I28" s="1">
+        <v>271.76</v>
+      </c>
+      <c r="J28">
+        <v>1.61</v>
+      </c>
+      <c r="K28" s="1">
+        <v>276.92</v>
+      </c>
+      <c r="L28" t="s">
+        <v>110</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29">
         <v>23.29</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29">
         <v>1.53</v>
       </c>
-      <c r="H28">
+      <c r="I29" s="1">
         <v>35.63</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J29">
         <v>1.56</v>
       </c>
-      <c r="J28">
+      <c r="K29" s="1">
         <v>36.33</v>
       </c>
-      <c r="K28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29">
-        <v>172</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="H29">
-        <v>271.76</v>
-      </c>
-      <c r="I29" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="J29">
-        <v>276.92</v>
-      </c>
-      <c r="K29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29" t="s">
+        <v>111</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F30">
         <v>138.96</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30">
         <v>1.58</v>
       </c>
-      <c r="H30">
+      <c r="I30" s="1">
         <v>219.56</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30">
         <v>1.61</v>
       </c>
-      <c r="J30">
+      <c r="K30" s="1">
         <v>223.73</v>
       </c>
-      <c r="K30" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30" t="s">
+        <v>112</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F31">
         <v>28.21</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31">
         <v>0.67</v>
       </c>
-      <c r="H31">
+      <c r="I31" s="1">
         <v>18.9</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31">
         <v>0.68</v>
       </c>
-      <c r="J31">
+      <c r="K31" s="1">
         <v>19.18</v>
       </c>
-      <c r="K31" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31" t="s">
+        <v>113</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F32">
         <v>37.44</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" t="s">
+        <v>83</v>
+      </c>
+      <c r="H32">
         <v>1.53</v>
       </c>
-      <c r="H32">
+      <c r="I32" s="1">
         <v>57.28</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32">
         <v>1.56</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="1">
         <v>58.41</v>
       </c>
-      <c r="K32" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32" t="s">
+        <v>114</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F33">
         <v>33.75</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33">
         <v>1.53</v>
       </c>
-      <c r="H33">
+      <c r="I33" s="1">
         <v>51.64</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33">
         <v>1.56</v>
       </c>
-      <c r="J33">
+      <c r="K33" s="1">
         <v>52.65</v>
       </c>
-      <c r="K33" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33" t="s">
+        <v>115</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F34">
         <v>35.54</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34">
         <v>1.56</v>
       </c>
-      <c r="H34">
+      <c r="I34" s="1">
         <v>55.44</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34">
         <v>1.59</v>
       </c>
-      <c r="J34">
+      <c r="K34" s="1">
         <v>56.51</v>
       </c>
-      <c r="K34" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" t="s">
+        <v>116</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F35">
         <v>67.17</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35">
         <v>1.82</v>
       </c>
-      <c r="H35">
+      <c r="I35" s="1">
         <v>122.25</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35">
         <v>1.85</v>
       </c>
-      <c r="J35">
+      <c r="K35" s="1">
         <v>124.26</v>
       </c>
-      <c r="K35" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35" t="s">
+        <v>117</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F36">
         <v>42.77</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36">
         <v>1.52</v>
       </c>
-      <c r="H36">
+      <c r="I36" s="1">
         <v>65.01000000000001</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36">
         <v>1.55</v>
       </c>
-      <c r="J36">
+      <c r="K36" s="1">
         <v>66.29000000000001</v>
       </c>
-      <c r="K36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36" t="s">
+        <v>118</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F37">
         <v>70.38</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37">
         <v>1.56</v>
       </c>
-      <c r="H37">
+      <c r="I37" s="1">
         <v>109.79</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37">
         <v>1.59</v>
       </c>
-      <c r="J37">
+      <c r="K37" s="1">
         <v>111.9</v>
       </c>
-      <c r="K37" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37" t="s">
+        <v>119</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F38">
+        <v>25.31</v>
+      </c>
+      <c r="G38" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38">
+        <v>0.66</v>
+      </c>
+      <c r="I38" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="J38">
+        <v>0.67</v>
+      </c>
+      <c r="K38" s="1">
+        <v>16.96</v>
+      </c>
+      <c r="L38" t="s">
+        <v>120</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39">
         <v>29</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G39" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39">
         <v>1.52</v>
       </c>
-      <c r="H38">
+      <c r="I39" s="1">
         <v>44.08</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J39">
         <v>1.55</v>
       </c>
-      <c r="J38">
+      <c r="K39" s="1">
         <v>44.95</v>
       </c>
-      <c r="K38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39">
-        <v>25.31</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="H39">
-        <v>16.7</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="J39">
-        <v>16.96</v>
-      </c>
-      <c r="K39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39" t="s">
+        <v>121</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E40" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F40">
         <v>51.72</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40">
         <v>1.84</v>
       </c>
-      <c r="H40">
+      <c r="I40" s="1">
         <v>95.16</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40">
         <v>1.87</v>
       </c>
-      <c r="J40">
+      <c r="K40" s="1">
         <v>96.72</v>
       </c>
-      <c r="K40" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40" t="s">
+        <v>122</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F41">
         <v>38.05</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41">
         <v>1.55</v>
       </c>
-      <c r="H41">
+      <c r="I41" s="1">
         <v>58.98</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41">
         <v>1.58</v>
       </c>
-      <c r="J41">
+      <c r="K41" s="1">
         <v>60.12</v>
       </c>
-      <c r="K41" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41" t="s">
+        <v>123</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F42">
         <v>32.31</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42">
         <v>1.52</v>
       </c>
-      <c r="H42">
+      <c r="I42" s="1">
         <v>49.11</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42">
         <v>1.55</v>
       </c>
-      <c r="J42">
+      <c r="K42" s="1">
         <v>50.08</v>
       </c>
-      <c r="K42" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42" t="s">
+        <v>124</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E43" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F43">
         <v>48.06</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43">
         <v>1.53</v>
       </c>
-      <c r="H43">
+      <c r="I43" s="1">
         <v>73.53</v>
       </c>
-      <c r="I43" s="1">
+      <c r="J43">
         <v>1.56</v>
       </c>
-      <c r="J43">
+      <c r="K43" s="1">
         <v>74.97</v>
       </c>
-      <c r="K43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43" t="s">
+        <v>125</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F44">
         <v>122.01</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44">
         <v>1.53</v>
       </c>
-      <c r="H44">
+      <c r="I44" s="1">
         <v>186.68</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44">
         <v>1.56</v>
       </c>
-      <c r="J44">
+      <c r="K44" s="1">
         <v>190.34</v>
       </c>
-      <c r="K44" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44" t="s">
+        <v>126</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E45" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F45">
         <v>50</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45">
         <v>1.77</v>
       </c>
-      <c r="H45">
+      <c r="I45" s="1">
         <v>88.5</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45">
         <v>1.8</v>
       </c>
-      <c r="J45">
+      <c r="K45" s="1">
         <v>90</v>
       </c>
-      <c r="K45" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="L45" t="s">
+        <v>127</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E46" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F46">
         <v>41.19</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G46" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46">
         <v>1.49</v>
       </c>
-      <c r="H46">
+      <c r="I46" s="1">
         <v>61.37</v>
       </c>
-      <c r="I46" s="1">
+      <c r="J46">
         <v>1.52</v>
       </c>
-      <c r="J46">
+      <c r="K46" s="1">
         <v>62.61</v>
       </c>
-      <c r="K46" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46" t="s">
+        <v>128</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E47" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F47">
         <v>115.63</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47">
         <v>1.49</v>
       </c>
-      <c r="H47">
+      <c r="I47" s="1">
         <v>172.29</v>
       </c>
-      <c r="I47" s="1">
+      <c r="J47">
         <v>1.52</v>
       </c>
-      <c r="J47">
+      <c r="K47" s="1">
         <v>175.76</v>
       </c>
-      <c r="K47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47" t="s">
+        <v>104</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48">
+        <v>35</v>
+      </c>
+      <c r="G48" t="s">
+        <v>83</v>
+      </c>
+      <c r="H48">
+        <v>1.48</v>
+      </c>
+      <c r="I48" s="1">
+        <v>51.8</v>
+      </c>
+      <c r="J48">
+        <v>1.51</v>
+      </c>
+      <c r="K48" s="1">
+        <v>52.85</v>
+      </c>
+      <c r="L48" t="s">
+        <v>129</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
         <v>32</v>
       </c>
-      <c r="C48" t="s">
-        <v>37</v>
-      </c>
-      <c r="D48" t="s">
-        <v>55</v>
-      </c>
-      <c r="E48" t="s">
-        <v>73</v>
-      </c>
-      <c r="F48">
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>80</v>
+      </c>
+      <c r="F49">
         <v>28.29</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49">
         <v>1.48</v>
       </c>
-      <c r="H48">
+      <c r="I49" s="1">
         <v>41.87</v>
       </c>
-      <c r="I48" s="1">
+      <c r="J49">
         <v>1.51</v>
       </c>
-      <c r="J48">
+      <c r="K49" s="1">
         <v>42.72</v>
       </c>
-      <c r="K48" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="L49" t="s">
+        <v>130</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
         <v>32</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" t="s">
+        <v>80</v>
+      </c>
+      <c r="F50">
+        <v>42.06</v>
+      </c>
+      <c r="G50" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50">
+        <v>1.48</v>
+      </c>
+      <c r="I50" s="1">
+        <v>62.25</v>
+      </c>
+      <c r="J50">
+        <v>1.51</v>
+      </c>
+      <c r="K50" s="1">
+        <v>63.51</v>
+      </c>
+      <c r="L50" t="s">
+        <v>131</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" t="s">
         <v>43</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D51" t="s">
         <v>61</v>
       </c>
-      <c r="E49" t="s">
-        <v>73</v>
-      </c>
-      <c r="F49">
-        <v>42.06</v>
-      </c>
-      <c r="G49" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H49">
-        <v>62.25</v>
-      </c>
-      <c r="I49" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J49">
-        <v>63.51</v>
-      </c>
-      <c r="K49" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" t="s">
-        <v>29</v>
-      </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" t="s">
-        <v>62</v>
-      </c>
-      <c r="E50" t="s">
-        <v>73</v>
-      </c>
-      <c r="F50">
-        <v>35</v>
-      </c>
-      <c r="G50" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H50">
-        <v>51.8</v>
-      </c>
-      <c r="I50" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J50">
-        <v>52.85</v>
-      </c>
-      <c r="K50" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" t="s">
-        <v>40</v>
-      </c>
-      <c r="D51" t="s">
-        <v>58</v>
-      </c>
       <c r="E51" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F51">
         <v>56.9</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G51" t="s">
+        <v>83</v>
+      </c>
+      <c r="H51">
         <v>1.49</v>
       </c>
-      <c r="H51">
+      <c r="I51" s="1">
         <v>84.78</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51">
         <v>1.52</v>
       </c>
-      <c r="J51">
+      <c r="K51" s="1">
         <v>86.48999999999999</v>
       </c>
-      <c r="K51" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="L51" t="s">
+        <v>132</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F52">
         <v>138</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52" t="s">
+        <v>83</v>
+      </c>
+      <c r="H52">
         <v>1.48</v>
       </c>
-      <c r="H52">
+      <c r="I52" s="1">
         <v>204.24</v>
       </c>
-      <c r="I52" s="1">
+      <c r="J52">
         <v>1.51</v>
       </c>
-      <c r="J52">
+      <c r="K52" s="1">
         <v>208.38</v>
       </c>
-      <c r="K52" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="L52" t="s">
+        <v>133</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F53">
         <v>31.91</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53" t="s">
+        <v>83</v>
+      </c>
+      <c r="H53">
         <v>0.65</v>
       </c>
-      <c r="H53">
+      <c r="I53" s="1">
         <v>20.74</v>
       </c>
-      <c r="I53" s="1">
+      <c r="J53">
         <v>0.66</v>
       </c>
-      <c r="J53">
+      <c r="K53" s="1">
         <v>21.06</v>
       </c>
-      <c r="K53" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="L53" t="s">
+        <v>134</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D54" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E54" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F54">
         <v>59.57</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54" t="s">
+        <v>83</v>
+      </c>
+      <c r="H54">
         <v>1.74</v>
       </c>
-      <c r="H54">
+      <c r="I54" s="1">
         <v>103.65</v>
       </c>
-      <c r="I54" s="1">
+      <c r="J54">
         <v>1.77</v>
       </c>
-      <c r="J54">
+      <c r="K54" s="1">
         <v>105.44</v>
       </c>
-      <c r="K54" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54" t="s">
+        <v>135</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C55" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E55" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F55">
         <v>28.16</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55" t="s">
+        <v>83</v>
+      </c>
+      <c r="H55">
         <v>1.48</v>
       </c>
-      <c r="H55">
+      <c r="I55" s="1">
         <v>41.68</v>
       </c>
-      <c r="I55" s="1">
+      <c r="J55">
         <v>1.51</v>
       </c>
-      <c r="J55">
+      <c r="K55" s="1">
         <v>42.52</v>
       </c>
-      <c r="K55" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="A60" s="5" t="s">
+      <c r="L55" t="s">
+        <v>136</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56">
+        <v>107</v>
+      </c>
+      <c r="G56" t="s">
+        <v>83</v>
+      </c>
+      <c r="H56">
+        <v>1.48</v>
+      </c>
+      <c r="I56" s="1">
+        <v>158.36</v>
+      </c>
+      <c r="J56">
+        <v>1.51</v>
+      </c>
+      <c r="K56" s="1">
+        <v>161.57</v>
+      </c>
+      <c r="L56" t="s">
+        <v>110</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57">
+        <v>31.49</v>
+      </c>
+      <c r="G57" t="s">
+        <v>83</v>
+      </c>
+      <c r="H57">
+        <v>1.48</v>
+      </c>
+      <c r="I57" s="1">
+        <v>46.61</v>
+      </c>
+      <c r="J57">
+        <v>1.51</v>
+      </c>
+      <c r="K57" s="1">
+        <v>47.55</v>
+      </c>
+      <c r="L57" t="s">
+        <v>137</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" t="s">
         <v>74</v>
       </c>
-      <c r="B60" s="6">
-        <v>1794.71</v>
-      </c>
-      <c r="C60" s="6">
-        <v>22</v>
-      </c>
-      <c r="D60" s="7">
-        <v>1.5787</v>
-      </c>
-      <c r="E60" s="6">
-        <v>2833.23</v>
-      </c>
-      <c r="F60" s="6">
-        <v>2887.08</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="6">
-        <v>663</v>
-      </c>
-      <c r="C61" s="6">
-        <v>21</v>
-      </c>
-      <c r="D61" s="7">
-        <v>1.5213</v>
-      </c>
-      <c r="E61" s="6">
-        <v>1008.64</v>
-      </c>
-      <c r="F61" s="6">
-        <v>1028.52</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="A62" s="5" t="s">
+      <c r="E58" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="G58" t="s">
+        <v>83</v>
+      </c>
+      <c r="H58">
+        <v>1.48</v>
+      </c>
+      <c r="I58" s="1">
+        <v>98.41</v>
+      </c>
+      <c r="J58">
+        <v>1.51</v>
+      </c>
+      <c r="K58" s="1">
+        <v>100.4</v>
+      </c>
+      <c r="L58" t="s">
+        <v>138</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" t="s">
+        <v>62</v>
+      </c>
+      <c r="E59" t="s">
+        <v>79</v>
+      </c>
+      <c r="F59">
+        <v>132.01</v>
+      </c>
+      <c r="G59" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59">
+        <v>1.48</v>
+      </c>
+      <c r="I59" s="1">
+        <v>195.37</v>
+      </c>
+      <c r="J59">
+        <v>1.51</v>
+      </c>
+      <c r="K59" s="1">
+        <v>199.34</v>
+      </c>
+      <c r="L59" t="s">
+        <v>139</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" t="s">
+        <v>79</v>
+      </c>
+      <c r="F60">
+        <v>33.8</v>
+      </c>
+      <c r="G60" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60">
+        <v>1.48</v>
+      </c>
+      <c r="I60" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="J60">
+        <v>1.51</v>
+      </c>
+      <c r="K60" s="1">
+        <v>51.04</v>
+      </c>
+      <c r="L60" t="s">
+        <v>140</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" t="s">
+        <v>80</v>
+      </c>
+      <c r="F61">
+        <v>44.92</v>
+      </c>
+      <c r="G61" t="s">
+        <v>83</v>
+      </c>
+      <c r="H61">
+        <v>1.47</v>
+      </c>
+      <c r="I61" s="1">
+        <v>66.03</v>
+      </c>
+      <c r="J61">
+        <v>1.5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>67.38</v>
+      </c>
+      <c r="L61" t="s">
+        <v>141</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" t="s">
+        <v>80</v>
+      </c>
+      <c r="F62">
+        <v>35.99</v>
+      </c>
+      <c r="G62" t="s">
+        <v>83</v>
+      </c>
+      <c r="H62">
+        <v>1.47</v>
+      </c>
+      <c r="I62" s="1">
+        <v>52.91</v>
+      </c>
+      <c r="J62">
+        <v>1.5</v>
+      </c>
+      <c r="K62" s="1">
+        <v>53.98</v>
+      </c>
+      <c r="L62" t="s">
+        <v>142</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" t="s">
+        <v>58</v>
+      </c>
+      <c r="D63" t="s">
         <v>76</v>
       </c>
-      <c r="B62" s="6">
+      <c r="E63" t="s">
+        <v>79</v>
+      </c>
+      <c r="F63">
+        <v>34.64</v>
+      </c>
+      <c r="G63" t="s">
+        <v>83</v>
+      </c>
+      <c r="H63">
+        <v>1.48</v>
+      </c>
+      <c r="I63" s="1">
+        <v>51.27</v>
+      </c>
+      <c r="J63">
+        <v>1.51</v>
+      </c>
+      <c r="K63" s="1">
+        <v>52.31</v>
+      </c>
+      <c r="L63" t="s">
+        <v>143</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" t="s">
+        <v>80</v>
+      </c>
+      <c r="F64">
+        <v>30.69</v>
+      </c>
+      <c r="G64" t="s">
+        <v>83</v>
+      </c>
+      <c r="H64">
+        <v>1.47</v>
+      </c>
+      <c r="I64" s="1">
+        <v>45.11</v>
+      </c>
+      <c r="J64">
+        <v>1.5</v>
+      </c>
+      <c r="K64" s="1">
+        <v>46.04</v>
+      </c>
+      <c r="L64" t="s">
+        <v>103</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="6">
+        <v>2200.14</v>
+      </c>
+      <c r="C69" s="6">
+        <v>28</v>
+      </c>
+      <c r="D69" s="7">
+        <v>1.5605</v>
+      </c>
+      <c r="E69" s="6">
+        <v>3433.27</v>
+      </c>
+      <c r="F69" s="6">
+        <v>3499.29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="6">
+        <v>774.6</v>
+      </c>
+      <c r="C70" s="6">
+        <v>24</v>
+      </c>
+      <c r="D70" s="7">
+        <v>1.5139</v>
+      </c>
+      <c r="E70" s="6">
+        <v>1172.69</v>
+      </c>
+      <c r="F70" s="6">
+        <v>1195.92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="6">
         <v>361.17</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C71" s="6">
         <v>6</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D71" s="7">
         <v>1.8175</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E71" s="6">
         <v>656.4400000000001</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F71" s="6">
         <v>667.27</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B63" s="6">
+    <row r="72" spans="1:6">
+      <c r="A72" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" s="6">
         <v>138.94</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C72" s="6">
         <v>5</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D72" s="7">
         <v>0.6843</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E72" s="6">
         <v>95.08</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F72" s="6">
         <v>96.48</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B64" s="9">
-        <v>2957.82</v>
-      </c>
-      <c r="C64" s="9">
-        <v>54</v>
-      </c>
-      <c r="D64" s="7"/>
-      <c r="E64" s="9">
-        <v>4593.39</v>
-      </c>
-      <c r="F64" s="9">
-        <v>4679.35</v>
+    <row r="73" spans="1:6">
+      <c r="A73" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B73" s="9">
+        <v>3474.85</v>
+      </c>
+      <c r="C73" s="9">
+        <v>63</v>
+      </c>
+      <c r="D73" s="7"/>
+      <c r="E73" s="9">
+        <v>5357.48</v>
+      </c>
+      <c r="F73" s="9">
+        <v>5458.96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A67:F67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="97">
   <si>
     <t>Дата</t>
   </si>
@@ -55,259 +55,238 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>София България</t>
-  </si>
-  <si>
-    <t>Търговище</t>
-  </si>
-  <si>
-    <t>В9933СМ</t>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>В2278РВ</t>
   </si>
   <si>
     <t>В6431НР</t>
   </si>
   <si>
+    <t>В6613КС</t>
+  </si>
+  <si>
+    <t>В4239ВТ</t>
+  </si>
+  <si>
+    <t>В8636СТ</t>
+  </si>
+  <si>
+    <t>В5089РВ</t>
+  </si>
+  <si>
+    <t>В7341ВС</t>
+  </si>
+  <si>
+    <t>В1283НТ</t>
+  </si>
+  <si>
+    <t>В2429ТТ</t>
+  </si>
+  <si>
+    <t>B6947НТ</t>
+  </si>
+  <si>
+    <t>В5116РС</t>
+  </si>
+  <si>
+    <t>В5163ХВ</t>
+  </si>
+  <si>
     <t>В6476ВС</t>
   </si>
   <si>
-    <t>B6947НТ</t>
-  </si>
-  <si>
-    <t>В5089РВ</t>
-  </si>
-  <si>
-    <t>В6613КС</t>
-  </si>
-  <si>
-    <t>В2429ТТ</t>
+    <t>В5654ВН</t>
+  </si>
+  <si>
+    <t>В6915ВХ</t>
+  </si>
+  <si>
+    <t>В5328РМ</t>
   </si>
   <si>
     <t>В4692РС</t>
   </si>
   <si>
-    <t>В6196РС</t>
-  </si>
-  <si>
-    <t>В7341ВС</t>
-  </si>
-  <si>
-    <t>В5654ВН</t>
-  </si>
-  <si>
-    <t>В1293НН</t>
-  </si>
-  <si>
-    <t>В5328РМ</t>
-  </si>
-  <si>
-    <t>В5163ХВ</t>
-  </si>
-  <si>
-    <t>В4239ВТ</t>
-  </si>
-  <si>
-    <t>В1283НТ</t>
-  </si>
-  <si>
-    <t>В8636СТ</t>
-  </si>
-  <si>
-    <t>78970155027722176</t>
+    <t>78970155027722226</t>
   </si>
   <si>
     <t>78970155027722358</t>
   </si>
   <si>
+    <t>78970155027722168</t>
+  </si>
+  <si>
+    <t>78970155027722325</t>
+  </si>
+  <si>
+    <t>78970155027722184</t>
+  </si>
+  <si>
+    <t>78970155027722382</t>
+  </si>
+  <si>
+    <t>78970155027722390</t>
+  </si>
+  <si>
+    <t>78970155027722333</t>
+  </si>
+  <si>
+    <t>78970155027722408</t>
+  </si>
+  <si>
+    <t>78970155027722416</t>
+  </si>
+  <si>
+    <t>78970155027722267</t>
+  </si>
+  <si>
+    <t>78970155027722374</t>
+  </si>
+  <si>
     <t>78970155027722283</t>
   </si>
   <si>
-    <t>78970155027722416</t>
-  </si>
-  <si>
-    <t>78970155027722382</t>
-  </si>
-  <si>
-    <t>78970155027722168</t>
-  </si>
-  <si>
-    <t>78970155027722408</t>
+    <t>78970155027722309</t>
+  </si>
+  <si>
+    <t>78970155027722291</t>
+  </si>
+  <si>
+    <t>78970155027722259</t>
   </si>
   <si>
     <t>78970155027722234</t>
   </si>
   <si>
-    <t>78970155027722424</t>
-  </si>
-  <si>
-    <t>78970155027722390</t>
-  </si>
-  <si>
-    <t>78970155027722309</t>
-  </si>
-  <si>
-    <t>78970155027722432</t>
-  </si>
-  <si>
-    <t>78970155027722259</t>
-  </si>
-  <si>
-    <t>78970155027722374</t>
-  </si>
-  <si>
-    <t>78970155027722325</t>
-  </si>
-  <si>
-    <t>78970155027722333</t>
-  </si>
-  <si>
-    <t>78970155027722184</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>DIESEL DOUBLE FILTER</t>
+  </si>
+  <si>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
-  </si>
-  <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>11:21</t>
-  </si>
-  <si>
-    <t>15:42</t>
-  </si>
-  <si>
-    <t>10:38</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>18:51</t>
-  </si>
-  <si>
-    <t>09:46</t>
-  </si>
-  <si>
-    <t>14:27</t>
-  </si>
-  <si>
-    <t>08:49</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>17:32</t>
-  </si>
-  <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>14:18</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>17:17</t>
-  </si>
-  <si>
-    <t>08:38</t>
-  </si>
-  <si>
-    <t>09:32</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>19:01</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:14</t>
-  </si>
-  <si>
-    <t>16:17</t>
-  </si>
-  <si>
-    <t>11:24</t>
-  </si>
-  <si>
-    <t>13:34</t>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>12:14</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>14:17</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>14:34</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>17:33</t>
+  </si>
+  <si>
+    <t>14:36</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 1</t>
@@ -725,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -789,40 +768,40 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F2">
-        <v>35.54</v>
+        <v>23.97</v>
       </c>
       <c r="G2" s="1">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="H2">
-        <v>55.44</v>
+        <v>35.24</v>
       </c>
       <c r="I2" s="1">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="J2">
-        <v>56.51</v>
+        <v>35.96</v>
       </c>
       <c r="K2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L2">
-        <v>65992</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>115490</v>
+        <v>121086</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -830,81 +809,81 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F3">
-        <v>67.17</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G3" s="1">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="H3">
-        <v>124.26</v>
+        <v>119.55</v>
       </c>
       <c r="I3" s="1">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="J3">
-        <v>124.26</v>
+        <v>119.55</v>
       </c>
       <c r="K3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>200309</v>
+        <v>122136</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F4">
-        <v>42.77</v>
+        <v>29.5</v>
       </c>
       <c r="G4" s="1">
-        <v>1.52</v>
+        <v>0.65</v>
       </c>
       <c r="H4">
-        <v>65.01000000000001</v>
+        <v>19.18</v>
       </c>
       <c r="I4" s="1">
-        <v>1.55</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>66.29000000000001</v>
+        <v>19.47</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>115876</v>
+        <v>208968</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -912,40 +891,40 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5">
-        <v>70.38</v>
+        <v>44.2</v>
       </c>
       <c r="G5" s="1">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="H5">
-        <v>109.79</v>
+        <v>65.42</v>
       </c>
       <c r="I5" s="1">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="J5">
-        <v>111.9</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>115942</v>
+        <v>121528</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -953,40 +932,40 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>26.49</v>
       </c>
       <c r="G6" s="1">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="H6">
-        <v>44.08</v>
+        <v>39.21</v>
       </c>
       <c r="I6" s="1">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>44.95</v>
+        <v>40</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>200867</v>
+        <v>121593</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -994,163 +973,163 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>25.31</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1">
-        <v>0.66</v>
+        <v>1.47</v>
       </c>
       <c r="H7">
-        <v>16.7</v>
+        <v>45.57</v>
       </c>
       <c r="I7" s="1">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="J7">
-        <v>16.96</v>
+        <v>46.5</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>116052</v>
+        <v>121634</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>64</v>
       </c>
       <c r="F8">
-        <v>51.72</v>
+        <v>116</v>
       </c>
       <c r="G8" s="1">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="H8">
-        <v>96.72</v>
+        <v>171.68</v>
       </c>
       <c r="I8" s="1">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="J8">
-        <v>96.72</v>
+        <v>175.16</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>293557</v>
+        <v>122045</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F9">
-        <v>38.05</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="H9">
-        <v>58.98</v>
+        <v>44.1</v>
       </c>
       <c r="I9" s="1">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="J9">
-        <v>60.12</v>
+        <v>45</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>116213</v>
+        <v>211614</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F10">
-        <v>32.31</v>
+        <v>61.29</v>
       </c>
       <c r="G10" s="1">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="H10">
-        <v>49.11</v>
+        <v>109.1</v>
       </c>
       <c r="I10" s="1">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="J10">
-        <v>50.08</v>
+        <v>109.1</v>
       </c>
       <c r="K10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>201368</v>
+        <v>122989</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1158,40 +1137,40 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11">
-        <v>48.06</v>
-      </c>
       <c r="G11" s="1">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="H11">
-        <v>73.53</v>
+        <v>38.74</v>
       </c>
       <c r="I11" s="1">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="J11">
-        <v>74.97</v>
+        <v>39.52</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>201756</v>
+        <v>211772</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1199,40 +1178,40 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F12">
-        <v>122.01</v>
+        <v>56.22</v>
       </c>
       <c r="G12" s="1">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="H12">
-        <v>186.68</v>
+        <v>83.77</v>
       </c>
       <c r="I12" s="1">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="J12">
-        <v>190.34</v>
+        <v>85.45</v>
       </c>
       <c r="K12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>201858</v>
+        <v>123104</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1240,163 +1219,163 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>21.94</v>
       </c>
       <c r="G13" s="1">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="H13">
-        <v>90</v>
+        <v>32.25</v>
       </c>
       <c r="I13" s="1">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J13">
-        <v>90</v>
+        <v>32.91</v>
       </c>
       <c r="K13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>215010</v>
+        <v>212288</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F14">
-        <v>41.19</v>
+        <v>47.95</v>
       </c>
       <c r="G14" s="1">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H14">
-        <v>61.37</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="I14" s="1">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="J14">
-        <v>62.61</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>117752</v>
+        <v>212293</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F15">
-        <v>115.63</v>
+        <v>34</v>
       </c>
       <c r="G15" s="1">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H15">
-        <v>172.29</v>
+        <v>49.98</v>
       </c>
       <c r="I15" s="1">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="J15">
-        <v>175.76</v>
+        <v>51</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>203469</v>
+        <v>123433</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F16">
-        <v>28.29</v>
+        <v>41.45</v>
       </c>
       <c r="G16" s="1">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H16">
-        <v>41.87</v>
+        <v>60.52</v>
       </c>
       <c r="I16" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J16">
-        <v>42.72</v>
+        <v>61.76</v>
       </c>
       <c r="K16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L16">
-        <v>85570</v>
+        <v>6068</v>
       </c>
       <c r="M16">
-        <v>204000</v>
+        <v>212689</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1404,40 +1383,40 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17">
-        <v>42.06</v>
+        <v>146</v>
       </c>
       <c r="G17" s="1">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H17">
-        <v>62.25</v>
+        <v>217.54</v>
       </c>
       <c r="I17" s="1">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J17">
-        <v>63.51</v>
+        <v>221.92</v>
       </c>
       <c r="K17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>118213</v>
+        <v>124132</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1445,81 +1424,81 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F18">
-        <v>35</v>
+        <v>37.94</v>
       </c>
       <c r="G18" s="1">
-        <v>1.48</v>
+        <v>0.62</v>
       </c>
       <c r="H18">
-        <v>51.8</v>
+        <v>23.52</v>
       </c>
       <c r="I18" s="1">
-        <v>1.51</v>
+        <v>0.63</v>
       </c>
       <c r="J18">
-        <v>52.85</v>
+        <v>23.9</v>
       </c>
       <c r="K18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L18">
-        <v>73832</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>204054</v>
+        <v>124232</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19">
-        <v>56.9</v>
+        <v>32.35</v>
       </c>
       <c r="G19" s="1">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H19">
-        <v>84.78</v>
+        <v>48.85</v>
       </c>
       <c r="I19" s="1">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="J19">
-        <v>86.48999999999999</v>
+        <v>49.82</v>
       </c>
       <c r="K19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>118260</v>
+        <v>213994</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1527,81 +1506,81 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F20">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="G20" s="1">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H20">
-        <v>204.24</v>
+        <v>45.26</v>
       </c>
       <c r="I20" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J20">
-        <v>208.38</v>
+        <v>46.19</v>
       </c>
       <c r="K20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>204494</v>
+        <v>124636</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F21">
-        <v>31.91</v>
+        <v>18.03</v>
       </c>
       <c r="G21" s="1">
-        <v>0.65</v>
+        <v>1.46</v>
       </c>
       <c r="H21">
-        <v>20.74</v>
+        <v>26.32</v>
       </c>
       <c r="I21" s="1">
-        <v>0.66</v>
+        <v>1.49</v>
       </c>
       <c r="J21">
-        <v>21.06</v>
+        <v>26.86</v>
       </c>
       <c r="K21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>118717</v>
+        <v>215932</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1609,40 +1588,40 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
         <v>64</v>
       </c>
       <c r="F22">
-        <v>59.57</v>
+        <v>143</v>
       </c>
       <c r="G22" s="1">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="H22">
-        <v>105.44</v>
+        <v>218.79</v>
       </c>
       <c r="I22" s="1">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="J22">
-        <v>105.44</v>
+        <v>223.08</v>
       </c>
       <c r="K22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>204980</v>
+        <v>216006</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1650,81 +1629,81 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F23">
-        <v>28.16</v>
+        <v>33.84</v>
       </c>
       <c r="G23" s="1">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="H23">
-        <v>41.68</v>
+        <v>51.78</v>
       </c>
       <c r="I23" s="1">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="J23">
-        <v>42.52</v>
+        <v>52.79</v>
       </c>
       <c r="K23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>205046</v>
+        <v>216086</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F24">
-        <v>107</v>
+        <v>39.46</v>
       </c>
       <c r="G24" s="1">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H24">
-        <v>158.36</v>
+        <v>57.61</v>
       </c>
       <c r="I24" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J24">
-        <v>161.57</v>
+        <v>58.8</v>
       </c>
       <c r="K24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>118440</v>
       </c>
       <c r="M24">
-        <v>119188</v>
+        <v>216115</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1732,122 +1711,122 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F25">
-        <v>31.49</v>
+        <v>23</v>
       </c>
       <c r="G25" s="1">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H25">
-        <v>46.61</v>
+        <v>33.58</v>
       </c>
       <c r="I25" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J25">
-        <v>47.55</v>
+        <v>34.27</v>
       </c>
       <c r="K25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>206084</v>
+        <v>216507</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F26">
-        <v>66.48999999999999</v>
+        <v>40.82</v>
       </c>
       <c r="G26" s="1">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H26">
-        <v>98.41</v>
+        <v>59.6</v>
       </c>
       <c r="I26" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J26">
-        <v>100.4</v>
+        <v>60.82</v>
       </c>
       <c r="K26" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>207379</v>
+        <v>216702</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F27">
-        <v>132.01</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G27" s="1">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="H27">
-        <v>195.37</v>
+        <v>98.36</v>
       </c>
       <c r="I27" s="1">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="J27">
-        <v>199.34</v>
+        <v>100.29</v>
       </c>
       <c r="K27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>120372</v>
+        <v>216786</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1855,40 +1834,40 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28">
         <v>26</v>
       </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" t="s">
-        <v>63</v>
-      </c>
-      <c r="F28">
-        <v>33.8</v>
-      </c>
       <c r="G28" s="1">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H28">
-        <v>50.02</v>
+        <v>37.96</v>
       </c>
       <c r="I28" s="1">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J28">
-        <v>51.04</v>
+        <v>38.74</v>
       </c>
       <c r="K28" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>120440</v>
+        <v>126388</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1896,193 +1875,130 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F29">
-        <v>35.99</v>
+        <v>61.95</v>
       </c>
       <c r="G29" s="1">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="H29">
-        <v>52.91</v>
+        <v>96.02</v>
       </c>
       <c r="I29" s="1">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="J29">
-        <v>53.98</v>
+        <v>97.88</v>
       </c>
       <c r="K29" t="s">
+        <v>90</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>126397</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>207651</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30">
-        <v>44.92</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H30">
-        <v>66.03</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J30">
-        <v>67.38</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="D33" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>120506</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31">
-        <v>30.69</v>
-      </c>
-      <c r="G31" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H31">
-        <v>45.11</v>
-      </c>
-      <c r="I31" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J31">
-        <v>46.04</v>
-      </c>
-      <c r="K31" t="s">
-        <v>96</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>208152</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" t="s">
-        <v>63</v>
-      </c>
-      <c r="F32">
-        <v>34.64</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H32">
-        <v>51.27</v>
-      </c>
-      <c r="I32" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J32">
-        <v>52.31</v>
-      </c>
-      <c r="K32" t="s">
-        <v>97</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>208237</v>
+      <c r="E33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="6">
+        <v>750.34</v>
+      </c>
+      <c r="C34" s="6">
+        <v>11</v>
+      </c>
+      <c r="D34" s="7">
+        <v>1.5062</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1130.16</v>
+      </c>
+      <c r="F34" s="6">
+        <v>1152.65</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="A35" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="6">
+        <v>408.62</v>
+      </c>
+      <c r="C35" s="6">
+        <v>13</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1.4646</v>
+      </c>
+      <c r="E35" s="6">
+        <v>598.48</v>
+      </c>
+      <c r="F35" s="6">
+        <v>610.74</v>
+      </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>9</v>
+      <c r="A36" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="6">
+        <v>128.83</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1.7748</v>
+      </c>
+      <c r="E36" s="6">
+        <v>228.65</v>
+      </c>
+      <c r="F36" s="6">
+        <v>228.65</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2090,102 +2006,42 @@
         <v>63</v>
       </c>
       <c r="B37" s="6">
-        <v>1071.19</v>
+        <v>67.44</v>
       </c>
       <c r="C37" s="6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D37" s="7">
-        <v>1.5003</v>
+        <v>0.6332</v>
       </c>
       <c r="E37" s="6">
-        <v>1607.14</v>
+        <v>42.7</v>
       </c>
       <c r="F37" s="6">
-        <v>1639.29</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="6">
-        <v>349.19</v>
-      </c>
-      <c r="C38" s="6">
-        <v>10</v>
-      </c>
-      <c r="D38" s="7">
-        <v>1.4887</v>
-      </c>
-      <c r="E38" s="6">
-        <v>519.85</v>
-      </c>
-      <c r="F38" s="6">
-        <v>530.3200000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="6">
-        <v>228.46</v>
-      </c>
-      <c r="C39" s="6">
-        <v>4</v>
-      </c>
-      <c r="D39" s="7">
-        <v>1.8227</v>
-      </c>
-      <c r="E39" s="6">
-        <v>416.42</v>
-      </c>
-      <c r="F39" s="6">
-        <v>416.42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="6">
-        <v>57.22</v>
-      </c>
-      <c r="C40" s="6">
-        <v>2</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.6543</v>
-      </c>
-      <c r="E40" s="6">
-        <v>37.44</v>
-      </c>
-      <c r="F40" s="6">
-        <v>38.02</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" s="9">
-        <v>1706.06</v>
-      </c>
-      <c r="C41" s="9">
-        <v>31</v>
-      </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="9">
-        <v>2580.85</v>
-      </c>
-      <c r="F41" s="9">
-        <v>2624.05</v>
+      <c r="A38" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="9">
+        <v>1355.23</v>
+      </c>
+      <c r="C38" s="9">
+        <v>28</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="9">
+        <v>1999.99</v>
+      </c>
+      <c r="F38" s="9">
+        <v>2035.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
   <si>
     <t>Дата</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -88,13 +85,10 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В2278РВ</t>
@@ -202,7 +196,7 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
+    <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
@@ -211,82 +205,88 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>12:14</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>14:17</t>
-  </si>
-  <si>
-    <t>16:02</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>10:53</t>
-  </si>
-  <si>
-    <t>14:22</t>
-  </si>
-  <si>
-    <t>11:17</t>
-  </si>
-  <si>
-    <t>13:01</t>
-  </si>
-  <si>
-    <t>14:34</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>10:11</t>
-  </si>
-  <si>
-    <t>17:33</t>
-  </si>
-  <si>
-    <t>14:36</t>
+    <t>2026-07-01 10:57:07</t>
+  </si>
+  <si>
+    <t>2026-07-01 11:50:56</t>
+  </si>
+  <si>
+    <t>2026-07-01 14:05:38</t>
+  </si>
+  <si>
+    <t>2026-07-02 12:14:55</t>
+  </si>
+  <si>
+    <t>2026-07-02 14:14:38</t>
+  </si>
+  <si>
+    <t>2026-07-02 14:55:24</t>
+  </si>
+  <si>
+    <t>2026-07-03 13:42:32</t>
+  </si>
+  <si>
+    <t>2026-07-06 10:09:03</t>
+  </si>
+  <si>
+    <t>2026-07-06 11:25:37</t>
+  </si>
+  <si>
+    <t>2026-07-06 14:17:15</t>
+  </si>
+  <si>
+    <t>2026-07-06 16:02:57</t>
+  </si>
+  <si>
+    <t>2026-07-07 11:15:46</t>
+  </si>
+  <si>
+    <t>2026-07-07 11:20:17</t>
+  </si>
+  <si>
+    <t>2026-07-07 14:50:27</t>
+  </si>
+  <si>
+    <t>2026-07-08 07:56:09</t>
+  </si>
+  <si>
+    <t>2026-07-09 12:59:12</t>
+  </si>
+  <si>
+    <t>2026-07-09 17:05:51</t>
+  </si>
+  <si>
+    <t>2026-07-10 10:53:34</t>
+  </si>
+  <si>
+    <t>2026-07-10 14:22:06</t>
+  </si>
+  <si>
+    <t>2026-07-13 11:17:08</t>
+  </si>
+  <si>
+    <t>2026-07-13 13:01:54</t>
+  </si>
+  <si>
+    <t>2026-07-13 14:34:56</t>
+  </si>
+  <si>
+    <t>2026-07-13 15:34:19</t>
+  </si>
+  <si>
+    <t>2026-07-14 10:11:34</t>
+  </si>
+  <si>
+    <t>2026-07-14 14:55:01</t>
+  </si>
+  <si>
+    <t>2026-07-14 17:33:22</t>
+  </si>
+  <si>
+    <t>2026-07-15 14:22:35</t>
+  </si>
+  <si>
+    <t>2026-07-15 14:36:06</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 1</t>
@@ -704,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -717,12 +717,11 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -759,25 +758,22 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>23.97</v>
@@ -795,39 +791,36 @@
         <v>35.96</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>121086</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>67.54000000000001</v>
       </c>
       <c r="G3" s="1">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H3">
-        <v>119.55</v>
+        <v>117.52</v>
       </c>
       <c r="I3" s="1">
         <v>1.77</v>
@@ -836,30 +829,27 @@
         <v>119.55</v>
       </c>
       <c r="K3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>122136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F4">
         <v>29.5</v>
@@ -877,30 +867,27 @@
         <v>19.47</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>208968</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>44.2</v>
@@ -918,30 +905,27 @@
         <v>66.73999999999999</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>121528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>26.49</v>
@@ -959,30 +943,27 @@
         <v>40</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>121593</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F7">
         <v>31</v>
@@ -1000,30 +981,27 @@
         <v>46.5</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>121634</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F8">
         <v>116</v>
@@ -1041,30 +1019,27 @@
         <v>175.16</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>122045</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F9">
         <v>30</v>
@@ -1082,39 +1057,36 @@
         <v>45</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
-      <c r="M9">
-        <v>211614</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F10">
         <v>61.29</v>
       </c>
       <c r="G10" s="1">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H10">
-        <v>109.1</v>
+        <v>107.26</v>
       </c>
       <c r="I10" s="1">
         <v>1.78</v>
@@ -1123,30 +1095,27 @@
         <v>109.1</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
-      <c r="M10">
-        <v>122989</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F11">
         <v>26</v>
@@ -1164,30 +1133,27 @@
         <v>39.52</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
-      <c r="M11">
-        <v>211772</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F12">
         <v>56.22</v>
@@ -1205,30 +1171,27 @@
         <v>85.45</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
-      <c r="M12">
-        <v>123104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F13">
         <v>21.94</v>
@@ -1246,30 +1209,27 @@
         <v>32.91</v>
       </c>
       <c r="K13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
-      <c r="M13">
-        <v>212288</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F14">
         <v>47.95</v>
@@ -1287,30 +1247,27 @@
         <v>71.93000000000001</v>
       </c>
       <c r="K14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
-      <c r="M14">
-        <v>212293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F15">
         <v>34</v>
@@ -1328,30 +1285,27 @@
         <v>51</v>
       </c>
       <c r="K15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
-      <c r="M15">
-        <v>123433</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F16">
         <v>41.45</v>
@@ -1369,30 +1323,27 @@
         <v>61.76</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L16">
-        <v>6068</v>
-      </c>
-      <c r="M16">
-        <v>212689</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F17">
         <v>146</v>
@@ -1410,30 +1361,27 @@
         <v>221.92</v>
       </c>
       <c r="K17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
-      <c r="M17">
-        <v>124132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F18">
         <v>37.94</v>
@@ -1451,30 +1399,27 @@
         <v>23.9</v>
       </c>
       <c r="K18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
-      <c r="M18">
-        <v>124232</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F19">
         <v>32.35</v>
@@ -1492,30 +1437,27 @@
         <v>49.82</v>
       </c>
       <c r="K19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="M19">
-        <v>213994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20">
         <v>31</v>
@@ -1533,30 +1475,27 @@
         <v>46.19</v>
       </c>
       <c r="K20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="M20">
-        <v>124636</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F21">
         <v>18.03</v>
@@ -1574,30 +1513,27 @@
         <v>26.86</v>
       </c>
       <c r="K21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
-      <c r="M21">
-        <v>215932</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F22">
         <v>143</v>
@@ -1615,30 +1551,27 @@
         <v>223.08</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
-      <c r="M22">
-        <v>216006</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F23">
         <v>33.84</v>
@@ -1656,30 +1589,27 @@
         <v>52.79</v>
       </c>
       <c r="K23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
-      <c r="M23">
-        <v>216086</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F24">
         <v>39.46</v>
@@ -1697,30 +1627,27 @@
         <v>58.8</v>
       </c>
       <c r="K24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L24">
-        <v>118440</v>
-      </c>
-      <c r="M24">
-        <v>216115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" t="s">
         <v>59</v>
-      </c>
-      <c r="E25" t="s">
-        <v>61</v>
       </c>
       <c r="F25">
         <v>23</v>
@@ -1738,30 +1665,27 @@
         <v>34.27</v>
       </c>
       <c r="K25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
-      <c r="M25">
-        <v>216507</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F26">
         <v>40.82</v>
@@ -1779,30 +1703,27 @@
         <v>60.82</v>
       </c>
       <c r="K26" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
-      <c r="M26">
-        <v>216702</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F27">
         <v>64.29000000000001</v>
@@ -1820,30 +1741,27 @@
         <v>100.29</v>
       </c>
       <c r="K27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
-      <c r="M27">
-        <v>216786</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F28">
         <v>26</v>
@@ -1861,30 +1779,27 @@
         <v>38.74</v>
       </c>
       <c r="K28" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
-      <c r="M28">
-        <v>126388</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F29">
         <v>61.95</v>
@@ -1907,11 +1822,8 @@
       <c r="L29">
         <v>0</v>
       </c>
-      <c r="M29">
-        <v>126397</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="3" t="s">
         <v>91</v>
       </c>
@@ -1943,7 +1855,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B34" s="6">
         <v>750.34</v>
@@ -1963,7 +1875,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B35" s="6">
         <v>408.62</v>
@@ -1983,7 +1895,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B36" s="6">
         <v>128.83</v>
@@ -1992,10 +1904,10 @@
         <v>2</v>
       </c>
       <c r="D36" s="7">
-        <v>1.7748</v>
+        <v>1.7448</v>
       </c>
       <c r="E36" s="6">
-        <v>228.65</v>
+        <v>224.78</v>
       </c>
       <c r="F36" s="6">
         <v>228.65</v>
@@ -2003,7 +1915,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B37" s="6">
         <v>67.44</v>
@@ -2033,7 +1945,7 @@
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="9">
-        <v>1999.99</v>
+        <v>1996.12</v>
       </c>
       <c r="F38" s="9">
         <v>2035.41</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="209">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -85,10 +91,49 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>В6613КС</t>
   </si>
   <si>
     <t>В2278РВ</t>
@@ -97,9 +142,6 @@
     <t>В6431НР</t>
   </si>
   <si>
-    <t>В6613КС</t>
-  </si>
-  <si>
     <t>В4239ВТ</t>
   </si>
   <si>
@@ -142,15 +184,15 @@
     <t>В4692РС</t>
   </si>
   <si>
+    <t>78970155027722168</t>
+  </si>
+  <si>
     <t>78970155027722226</t>
   </si>
   <si>
     <t>78970155027722358</t>
   </si>
   <si>
-    <t>78970155027722168</t>
-  </si>
-  <si>
     <t>78970155027722325</t>
   </si>
   <si>
@@ -193,100 +235,394 @@
     <t>78970155027722234</t>
   </si>
   <si>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-01 10:57:07</t>
-  </si>
-  <si>
-    <t>2026-07-01 11:50:56</t>
-  </si>
-  <si>
-    <t>2026-07-01 14:05:38</t>
-  </si>
-  <si>
-    <t>2026-07-02 12:14:55</t>
-  </si>
-  <si>
-    <t>2026-07-02 14:14:38</t>
-  </si>
-  <si>
-    <t>2026-07-02 14:55:24</t>
-  </si>
-  <si>
-    <t>2026-07-03 13:42:32</t>
-  </si>
-  <si>
-    <t>2026-07-06 10:09:03</t>
-  </si>
-  <si>
-    <t>2026-07-06 11:25:37</t>
-  </si>
-  <si>
-    <t>2026-07-06 14:17:15</t>
-  </si>
-  <si>
-    <t>2026-07-06 16:02:57</t>
-  </si>
-  <si>
-    <t>2026-07-07 11:15:46</t>
-  </si>
-  <si>
-    <t>2026-07-07 11:20:17</t>
-  </si>
-  <si>
-    <t>2026-07-07 14:50:27</t>
-  </si>
-  <si>
-    <t>2026-07-08 07:56:09</t>
-  </si>
-  <si>
-    <t>2026-07-09 12:59:12</t>
-  </si>
-  <si>
-    <t>2026-07-09 17:05:51</t>
-  </si>
-  <si>
-    <t>2026-07-10 10:53:34</t>
-  </si>
-  <si>
-    <t>2026-07-10 14:22:06</t>
-  </si>
-  <si>
-    <t>2026-07-13 11:17:08</t>
-  </si>
-  <si>
-    <t>2026-07-13 13:01:54</t>
-  </si>
-  <si>
-    <t>2026-07-13 14:34:56</t>
-  </si>
-  <si>
-    <t>2026-07-13 15:34:19</t>
-  </si>
-  <si>
-    <t>2026-07-14 10:11:34</t>
-  </si>
-  <si>
-    <t>2026-07-14 14:55:01</t>
-  </si>
-  <si>
-    <t>2026-07-14 17:33:22</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:22:35</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:36:06</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:05:00</t>
+  </si>
+  <si>
+    <t>10:57:00</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>12:14:00</t>
+  </si>
+  <si>
+    <t>14:14:00</t>
+  </si>
+  <si>
+    <t>14:55:00</t>
+  </si>
+  <si>
+    <t>13:42:00</t>
+  </si>
+  <si>
+    <t>10:09:00</t>
+  </si>
+  <si>
+    <t>11:25:00</t>
+  </si>
+  <si>
+    <t>14:17:00</t>
+  </si>
+  <si>
+    <t>16:02:00</t>
+  </si>
+  <si>
+    <t>11:16:00</t>
+  </si>
+  <si>
+    <t>11:20:00</t>
+  </si>
+  <si>
+    <t>14:50:00</t>
+  </si>
+  <si>
+    <t>07:56:00</t>
+  </si>
+  <si>
+    <t>12:59:00</t>
+  </si>
+  <si>
+    <t>17:05:00</t>
+  </si>
+  <si>
+    <t>10:53:00</t>
+  </si>
+  <si>
+    <t>14:22:00</t>
+  </si>
+  <si>
+    <t>11:17:00</t>
+  </si>
+  <si>
+    <t>13:01:00</t>
+  </si>
+  <si>
+    <t>15:34:00</t>
+  </si>
+  <si>
+    <t>14:34:00</t>
+  </si>
+  <si>
+    <t>10:11:00</t>
+  </si>
+  <si>
+    <t>17:33:00</t>
+  </si>
+  <si>
+    <t>14:36:00</t>
+  </si>
+  <si>
+    <t>12:01:00</t>
+  </si>
+  <si>
+    <t>10:04:00</t>
+  </si>
+  <si>
+    <t>13:44:00</t>
+  </si>
+  <si>
+    <t>15:58:00</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>14:33:00</t>
+  </si>
+  <si>
+    <t>17:46:00</t>
+  </si>
+  <si>
+    <t>10:28:00</t>
+  </si>
+  <si>
+    <t>13:06:00</t>
+  </si>
+  <si>
+    <t>15:31:00</t>
+  </si>
+  <si>
+    <t>15:54:00</t>
+  </si>
+  <si>
+    <t>19:55:00</t>
+  </si>
+  <si>
+    <t>12:23:00</t>
+  </si>
+  <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>14:23:00</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>14:26:00</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
+    <t>17:15:00</t>
+  </si>
+  <si>
+    <t>10:24:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>12:36:00</t>
+  </si>
+  <si>
+    <t>08:14:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>09:46:00</t>
+  </si>
+  <si>
+    <t>11:56:00</t>
+  </si>
+  <si>
+    <t>12:41:00</t>
+  </si>
+  <si>
+    <t>13:33:00</t>
+  </si>
+  <si>
+    <t>14:52:00</t>
+  </si>
+  <si>
+    <t>16:23:00</t>
+  </si>
+  <si>
+    <t>10:26:00</t>
+  </si>
+  <si>
+    <t>10:47:00</t>
+  </si>
+  <si>
+    <t>15:24:00</t>
+  </si>
+  <si>
+    <t>20:57:00</t>
+  </si>
+  <si>
+    <t>3234129784 3234129784</t>
+  </si>
+  <si>
+    <t>3234149125 3234149125</t>
+  </si>
+  <si>
+    <t>3234146695 3234146695</t>
+  </si>
+  <si>
+    <t>3234197700 3234197700</t>
+  </si>
+  <si>
+    <t>3234198665 3234198665</t>
+  </si>
+  <si>
+    <t>3234200121 3234200121</t>
+  </si>
+  <si>
+    <t>3234250321 3234250321</t>
+  </si>
+  <si>
+    <t>3234389152 3234389152</t>
+  </si>
+  <si>
+    <t>3234391108 3234391108</t>
+  </si>
+  <si>
+    <t>3234391491 3234391491</t>
+  </si>
+  <si>
+    <t>3234395986 3234395986</t>
+  </si>
+  <si>
+    <t>3234410039 3234410039</t>
+  </si>
+  <si>
+    <t>3234436044 3234436044</t>
+  </si>
+  <si>
+    <t>3234441621 3234441621</t>
+  </si>
+  <si>
+    <t>3234465094 3234465094</t>
+  </si>
+  <si>
+    <t>3234531872 3234531872</t>
+  </si>
+  <si>
+    <t>3234534593 3234534593</t>
+  </si>
+  <si>
+    <t>3234606684 3234606684</t>
+  </si>
+  <si>
+    <t>3234609675 3234609675</t>
+  </si>
+  <si>
+    <t>3234733422 3234733422</t>
+  </si>
+  <si>
+    <t>3234739400 3234739400</t>
+  </si>
+  <si>
+    <t>3234740799 3234740799</t>
+  </si>
+  <si>
+    <t>3234741529 3234741529</t>
+  </si>
+  <si>
+    <t>3234764942 3234764942</t>
+  </si>
+  <si>
+    <t>3234788162 3234788162</t>
+  </si>
+  <si>
+    <t>3234792911 3234792911</t>
+  </si>
+  <si>
+    <t>3234809346 3234809346</t>
+  </si>
+  <si>
+    <t>3234835332 3234835332</t>
+  </si>
+  <si>
+    <t>3234881031 3234881031</t>
+  </si>
+  <si>
+    <t>3234881870 3234881870</t>
+  </si>
+  <si>
+    <t>3234888034 3234888034</t>
+  </si>
+  <si>
+    <t>3234891288 3234891288</t>
+  </si>
+  <si>
+    <t>3234935039 3234935039</t>
+  </si>
+  <si>
+    <t>3234941281 3234941281</t>
+  </si>
+  <si>
+    <t>3234943393 3234943393</t>
+  </si>
+  <si>
+    <t>3235088954 3235088954</t>
+  </si>
+  <si>
+    <t>3235091603 3235091603</t>
+  </si>
+  <si>
+    <t>3235142858 3235142858</t>
+  </si>
+  <si>
+    <t>3235144603 3235144603</t>
+  </si>
+  <si>
+    <t>3235150642 3235150642</t>
+  </si>
+  <si>
+    <t>3235184983 3235184983</t>
+  </si>
+  <si>
+    <t>3235185802 3235185802</t>
+  </si>
+  <si>
+    <t>3235188831 3235188831</t>
+  </si>
+  <si>
+    <t>3235233671 3235233671</t>
+  </si>
+  <si>
+    <t>3235234632 3235234632</t>
+  </si>
+  <si>
+    <t>3235237620 3235237620</t>
+  </si>
+  <si>
+    <t>3235238300 3235238300</t>
+  </si>
+  <si>
+    <t>3235242086 3235242086</t>
+  </si>
+  <si>
+    <t>3235262370 3235262370</t>
+  </si>
+  <si>
+    <t>3235283198 3235283198</t>
+  </si>
+  <si>
+    <t>3235285143 3235285143</t>
+  </si>
+  <si>
+    <t>3235425583 3235425583</t>
+  </si>
+  <si>
+    <t>3235436210 3235436210</t>
+  </si>
+  <si>
+    <t>3235480306 3235480306</t>
+  </si>
+  <si>
+    <t>3235525533 3235525533</t>
+  </si>
+  <si>
+    <t>3235526249 3235526249</t>
+  </si>
+  <si>
+    <t>3235528321 3235528321</t>
+  </si>
+  <si>
+    <t>3235528827 3235528827</t>
+  </si>
+  <si>
+    <t>3235530472 3235530472</t>
+  </si>
+  <si>
+    <t>3235534088 3235534088</t>
+  </si>
+  <si>
+    <t>3235572241 3235572241</t>
+  </si>
+  <si>
+    <t>3235632003 3235632003</t>
+  </si>
+  <si>
+    <t>3235635196 3235635196</t>
+  </si>
+  <si>
+    <t>3235653643 3235653643</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА АКСАКОВО % 1</t>
@@ -704,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -713,15 +1049,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -758,1202 +1096,2960 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2">
+        <v>29.5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2">
+        <v>0.65</v>
+      </c>
+      <c r="I2" s="1">
+        <v>19.18</v>
+      </c>
+      <c r="J2">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>19.47</v>
+      </c>
+      <c r="L2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3">
+        <v>23.97</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3">
+        <v>1.47</v>
+      </c>
+      <c r="I3" s="1">
+        <v>35.24</v>
+      </c>
+      <c r="J3">
+        <v>1.5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>35.96</v>
+      </c>
+      <c r="L3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4">
+        <v>1.74</v>
+      </c>
+      <c r="I4" s="1">
+        <v>117.52</v>
+      </c>
+      <c r="J4">
+        <v>1.77</v>
+      </c>
+      <c r="K4" s="1">
+        <v>119.55</v>
+      </c>
+      <c r="L4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D5" t="s">
         <v>59</v>
       </c>
-      <c r="F2">
-        <v>23.97</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H2">
-        <v>35.24</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
-        <v>35.96</v>
-      </c>
-      <c r="K2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="H3">
-        <v>117.52</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="J3">
-        <v>119.55</v>
-      </c>
-      <c r="K3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4">
-        <v>29.5</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H4">
-        <v>19.18</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J4">
-        <v>19.47</v>
-      </c>
-      <c r="K4" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F5">
         <v>44.2</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5">
         <v>1.48</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>65.42</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>66.73999999999999</v>
       </c>
-      <c r="K5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F6">
         <v>26.49</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6">
         <v>1.48</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>39.21</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.51</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>40</v>
       </c>
-      <c r="K6" t="s">
-        <v>67</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F7">
         <v>31</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7">
         <v>1.47</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>45.57</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.5</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>46.5</v>
       </c>
-      <c r="K7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>83</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F8">
         <v>116</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8">
         <v>1.48</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>171.68</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.51</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>175.16</v>
       </c>
-      <c r="K8" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F9">
         <v>30</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9">
         <v>1.47</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>44.1</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.5</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>45</v>
       </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F10">
         <v>61.29</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10">
         <v>1.75</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>107.26</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.78</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>109.1</v>
       </c>
-      <c r="K10" t="s">
-        <v>71</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="L10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F11">
         <v>26</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11">
         <v>1.49</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>38.74</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.52</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>39.52</v>
       </c>
-      <c r="K11" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="L11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F12">
         <v>56.22</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12">
         <v>1.49</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>83.77</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.52</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>85.45</v>
       </c>
-      <c r="K12" t="s">
-        <v>73</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="L12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F13">
         <v>21.94</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13">
         <v>1.47</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>32.25</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.5</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>32.91</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
         <v>74</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
       </c>
       <c r="F14">
         <v>47.95</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14">
         <v>1.47</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>70.48999999999999</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.5</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>71.93000000000001</v>
       </c>
-      <c r="K14" t="s">
-        <v>75</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="L14" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F15">
         <v>34</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15">
         <v>1.47</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>49.98</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.5</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>51</v>
       </c>
-      <c r="K15" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="L15" t="s">
+        <v>91</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F16">
         <v>41.45</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16">
         <v>1.46</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>60.52</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.49</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>61.76</v>
       </c>
-      <c r="K16" t="s">
-        <v>77</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="L16" t="s">
+        <v>92</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F17">
         <v>146</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17">
         <v>1.49</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>217.54</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.52</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>221.92</v>
       </c>
-      <c r="K17" t="s">
-        <v>78</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="L17" t="s">
+        <v>93</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F18">
         <v>37.94</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18">
         <v>0.62</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>23.52</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>0.63</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>23.9</v>
       </c>
-      <c r="K18" t="s">
-        <v>79</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="L18" t="s">
+        <v>94</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F19">
         <v>32.35</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19">
         <v>1.51</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>48.85</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.54</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>49.82</v>
       </c>
-      <c r="K19" t="s">
-        <v>80</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="L19" t="s">
+        <v>95</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F20">
         <v>31</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20">
         <v>1.46</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="1">
         <v>45.26</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20">
         <v>1.49</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>46.19</v>
       </c>
-      <c r="K20" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="L20" t="s">
+        <v>96</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F21">
         <v>18.03</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21">
         <v>1.46</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>26.32</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>1.49</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>26.86</v>
       </c>
-      <c r="K21" t="s">
-        <v>82</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="L21" t="s">
+        <v>97</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F22">
         <v>143</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22">
         <v>1.53</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="1">
         <v>218.79</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>1.56</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>223.08</v>
       </c>
-      <c r="K22" t="s">
-        <v>83</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="L22" t="s">
+        <v>98</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23">
+        <v>39.46</v>
+      </c>
+      <c r="G23" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23">
+        <v>1.46</v>
+      </c>
+      <c r="I23" s="1">
+        <v>57.61</v>
+      </c>
+      <c r="J23">
+        <v>1.49</v>
+      </c>
+      <c r="K23" s="1">
+        <v>58.8</v>
+      </c>
+      <c r="L23" t="s">
+        <v>99</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24">
+        <v>33.84</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24">
+        <v>1.53</v>
+      </c>
+      <c r="I24" s="1">
+        <v>51.78</v>
+      </c>
+      <c r="J24">
+        <v>1.56</v>
+      </c>
+      <c r="K24" s="1">
+        <v>52.79</v>
+      </c>
+      <c r="L24" t="s">
+        <v>100</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
         <v>23</v>
       </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23">
-        <v>33.84</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H23">
-        <v>51.78</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J23">
-        <v>52.79</v>
-      </c>
-      <c r="K23" t="s">
-        <v>84</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24">
-        <v>39.46</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H24">
-        <v>57.61</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J24">
-        <v>58.8</v>
-      </c>
-      <c r="K24" t="s">
-        <v>85</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F25">
         <v>23</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25">
         <v>1.46</v>
       </c>
-      <c r="H25">
+      <c r="I25" s="1">
         <v>33.58</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25">
         <v>1.49</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="1">
         <v>34.27</v>
       </c>
-      <c r="K25" t="s">
-        <v>86</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="L25" t="s">
+        <v>101</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F26">
         <v>40.82</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26">
         <v>1.46</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="1">
         <v>59.6</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26">
         <v>1.49</v>
       </c>
-      <c r="J26">
+      <c r="K26" s="1">
         <v>60.82</v>
       </c>
-      <c r="K26" t="s">
-        <v>87</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="L26" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F27">
         <v>64.29000000000001</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27">
         <v>1.53</v>
       </c>
-      <c r="H27">
+      <c r="I27" s="1">
         <v>98.36</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27">
         <v>1.56</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="1">
         <v>100.29</v>
       </c>
-      <c r="K27" t="s">
-        <v>88</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="L27" t="s">
+        <v>102</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F28">
         <v>26</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28">
         <v>1.46</v>
       </c>
-      <c r="H28">
+      <c r="I28" s="1">
         <v>37.96</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28">
         <v>1.49</v>
       </c>
-      <c r="J28">
+      <c r="K28" s="1">
         <v>38.74</v>
       </c>
-      <c r="K28" t="s">
-        <v>89</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="L28" t="s">
+        <v>96</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F29">
         <v>61.95</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29">
         <v>1.55</v>
       </c>
-      <c r="H29">
+      <c r="I29" s="1">
         <v>96.02</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29">
         <v>1.58</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="1">
         <v>97.88</v>
       </c>
-      <c r="K29" t="s">
-        <v>90</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="3" t="s">
+      <c r="L29" t="s">
+        <v>103</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30">
+        <v>19.99</v>
+      </c>
+      <c r="G30" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30">
+        <v>1.47</v>
+      </c>
+      <c r="I30" s="1">
+        <v>29.39</v>
+      </c>
+      <c r="J30">
+        <v>1.5</v>
+      </c>
+      <c r="K30" s="1">
+        <v>29.98</v>
+      </c>
+      <c r="L30" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31">
+        <v>33</v>
+      </c>
+      <c r="G31" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31">
+        <v>1.58</v>
+      </c>
+      <c r="I31" s="1">
+        <v>52.14</v>
+      </c>
+      <c r="J31">
+        <v>1.61</v>
+      </c>
+      <c r="K31" s="1">
+        <v>53.13</v>
+      </c>
+      <c r="L31" t="s">
+        <v>105</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32">
+        <v>16.46</v>
+      </c>
+      <c r="G32" t="s">
+        <v>77</v>
+      </c>
+      <c r="H32">
+        <v>1.47</v>
+      </c>
+      <c r="I32" s="1">
+        <v>24.2</v>
+      </c>
+      <c r="J32">
+        <v>1.5</v>
+      </c>
+      <c r="K32" s="1">
+        <v>24.69</v>
+      </c>
+      <c r="L32" t="s">
+        <v>106</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33">
+        <v>31.71</v>
+      </c>
+      <c r="G33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33">
+        <v>1.47</v>
+      </c>
+      <c r="I33" s="1">
+        <v>46.61</v>
+      </c>
+      <c r="J33">
+        <v>1.5</v>
+      </c>
+      <c r="K33" s="1">
+        <v>47.56</v>
+      </c>
+      <c r="L33" t="s">
+        <v>107</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34">
+        <v>54.62</v>
+      </c>
+      <c r="G34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34">
+        <v>1.86</v>
+      </c>
+      <c r="I34" s="1">
+        <v>101.59</v>
+      </c>
+      <c r="J34">
+        <v>1.89</v>
+      </c>
+      <c r="K34" s="1">
+        <v>103.23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>108</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35">
+        <v>31.59</v>
+      </c>
+      <c r="G35" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35">
+        <v>1.6</v>
+      </c>
+      <c r="I35" s="1">
+        <v>50.54</v>
+      </c>
+      <c r="J35">
+        <v>1.63</v>
+      </c>
+      <c r="K35" s="1">
+        <v>51.49</v>
+      </c>
+      <c r="L35" t="s">
+        <v>109</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36">
+        <v>41.12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36">
+        <v>0.63</v>
+      </c>
+      <c r="I36" s="1">
+        <v>25.91</v>
+      </c>
+      <c r="J36">
+        <v>0.64</v>
+      </c>
+      <c r="K36" s="1">
+        <v>26.32</v>
+      </c>
+      <c r="L36" t="s">
+        <v>110</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37">
+        <v>19.31</v>
+      </c>
+      <c r="G37" t="s">
+        <v>77</v>
+      </c>
+      <c r="H37">
+        <v>1.5</v>
+      </c>
+      <c r="I37" s="1">
+        <v>28.96</v>
+      </c>
+      <c r="J37">
+        <v>1.53</v>
+      </c>
+      <c r="K37" s="1">
+        <v>29.54</v>
+      </c>
+      <c r="L37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38">
+        <v>170.99</v>
+      </c>
+      <c r="G38" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38">
+        <v>1.65</v>
+      </c>
+      <c r="I38" s="1">
+        <v>282.13</v>
+      </c>
+      <c r="J38">
+        <v>1.68</v>
+      </c>
+      <c r="K38" s="1">
+        <v>287.26</v>
+      </c>
+      <c r="L38" t="s">
+        <v>112</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39">
+        <v>31</v>
+      </c>
+      <c r="G39" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39">
+        <v>1.5</v>
+      </c>
+      <c r="I39" s="1">
+        <v>46.5</v>
+      </c>
+      <c r="J39">
+        <v>1.53</v>
+      </c>
+      <c r="K39" s="1">
+        <v>47.43</v>
+      </c>
+      <c r="L39" t="s">
+        <v>113</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="G40" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40">
+        <v>1.65</v>
+      </c>
+      <c r="I40" s="1">
+        <v>109.33</v>
+      </c>
+      <c r="J40">
+        <v>1.68</v>
+      </c>
+      <c r="K40" s="1">
+        <v>111.32</v>
+      </c>
+      <c r="L40" t="s">
+        <v>114</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41">
+        <v>40.44</v>
+      </c>
+      <c r="G41" t="s">
+        <v>77</v>
+      </c>
+      <c r="H41">
+        <v>1.5</v>
+      </c>
+      <c r="I41" s="1">
+        <v>60.66</v>
+      </c>
+      <c r="J41">
+        <v>1.53</v>
+      </c>
+      <c r="K41" s="1">
+        <v>61.87</v>
+      </c>
+      <c r="L41" t="s">
+        <v>115</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42">
+        <v>24.8</v>
+      </c>
+      <c r="G42" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42">
+        <v>1.51</v>
+      </c>
+      <c r="I42" s="1">
+        <v>37.45</v>
+      </c>
+      <c r="J42">
+        <v>1.54</v>
+      </c>
+      <c r="K42" s="1">
+        <v>38.19</v>
+      </c>
+      <c r="L42" t="s">
+        <v>116</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43">
+        <v>21.81</v>
+      </c>
+      <c r="G43" t="s">
+        <v>77</v>
+      </c>
+      <c r="H43">
+        <v>1.51</v>
+      </c>
+      <c r="I43" s="1">
+        <v>32.93</v>
+      </c>
+      <c r="J43">
+        <v>1.54</v>
+      </c>
+      <c r="K43" s="1">
+        <v>33.59</v>
+      </c>
+      <c r="L43" t="s">
+        <v>117</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44">
+        <v>31.91</v>
+      </c>
+      <c r="G44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44">
+        <v>1.66</v>
+      </c>
+      <c r="I44" s="1">
+        <v>52.97</v>
+      </c>
+      <c r="J44">
+        <v>1.69</v>
+      </c>
+      <c r="K44" s="1">
+        <v>53.93</v>
+      </c>
+      <c r="L44" t="s">
+        <v>118</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45">
+        <v>15.69</v>
+      </c>
+      <c r="G45" t="s">
+        <v>77</v>
+      </c>
+      <c r="H45">
+        <v>1.67</v>
+      </c>
+      <c r="I45" s="1">
+        <v>26.2</v>
+      </c>
+      <c r="J45">
+        <v>1.7</v>
+      </c>
+      <c r="K45" s="1">
+        <v>26.67</v>
+      </c>
+      <c r="L45" t="s">
+        <v>119</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>75</v>
+      </c>
+      <c r="F46">
+        <v>64.72</v>
+      </c>
+      <c r="G46" t="s">
+        <v>77</v>
+      </c>
+      <c r="H46">
+        <v>1.93</v>
+      </c>
+      <c r="I46" s="1">
+        <v>124.91</v>
+      </c>
+      <c r="J46">
+        <v>1.96</v>
+      </c>
+      <c r="K46" s="1">
+        <v>126.85</v>
+      </c>
+      <c r="L46" t="s">
+        <v>120</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s">
+        <v>77</v>
+      </c>
+      <c r="H47">
+        <v>1.51</v>
+      </c>
+      <c r="I47" s="1">
+        <v>19.63</v>
+      </c>
+      <c r="J47">
+        <v>1.54</v>
+      </c>
+      <c r="K47" s="1">
+        <v>20.02</v>
+      </c>
+      <c r="L47" t="s">
+        <v>121</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" t="s">
+        <v>74</v>
+      </c>
+      <c r="F48">
+        <v>31.09</v>
+      </c>
+      <c r="G48" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48">
+        <v>1.51</v>
+      </c>
+      <c r="I48" s="1">
+        <v>46.95</v>
+      </c>
+      <c r="J48">
+        <v>1.54</v>
+      </c>
+      <c r="K48" s="1">
+        <v>47.88</v>
+      </c>
+      <c r="L48" t="s">
+        <v>122</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49">
+        <v>27.95</v>
+      </c>
+      <c r="G49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H49">
+        <v>0.63</v>
+      </c>
+      <c r="I49" s="1">
+        <v>17.61</v>
+      </c>
+      <c r="J49">
+        <v>0.64</v>
+      </c>
+      <c r="K49" s="1">
+        <v>17.89</v>
+      </c>
+      <c r="L49" t="s">
+        <v>123</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50">
+        <v>68.93000000000001</v>
+      </c>
+      <c r="G50" t="s">
+        <v>77</v>
+      </c>
+      <c r="H50">
+        <v>1.69</v>
+      </c>
+      <c r="I50" s="1">
+        <v>116.49</v>
+      </c>
+      <c r="J50">
+        <v>1.72</v>
+      </c>
+      <c r="K50" s="1">
+        <v>118.56</v>
+      </c>
+      <c r="L50" t="s">
+        <v>124</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51">
+        <v>29.33</v>
+      </c>
+      <c r="G51" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51">
+        <v>1.51</v>
+      </c>
+      <c r="I51" s="1">
+        <v>44.29</v>
+      </c>
+      <c r="J51">
+        <v>1.54</v>
+      </c>
+      <c r="K51" s="1">
+        <v>45.17</v>
+      </c>
+      <c r="L51" t="s">
+        <v>125</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" t="s">
+        <v>76</v>
+      </c>
+      <c r="F52">
+        <v>133.99</v>
+      </c>
+      <c r="G52" t="s">
+        <v>77</v>
+      </c>
+      <c r="H52">
+        <v>1.69</v>
+      </c>
+      <c r="I52" s="1">
+        <v>226.44</v>
+      </c>
+      <c r="J52">
+        <v>1.72</v>
+      </c>
+      <c r="K52" s="1">
+        <v>230.46</v>
+      </c>
+      <c r="L52" t="s">
+        <v>126</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" t="s">
+        <v>74</v>
+      </c>
+      <c r="F53">
+        <v>28.01</v>
+      </c>
+      <c r="G53" t="s">
+        <v>77</v>
+      </c>
+      <c r="H53">
+        <v>1.53</v>
+      </c>
+      <c r="I53" s="1">
+        <v>42.86</v>
+      </c>
+      <c r="J53">
+        <v>1.56</v>
+      </c>
+      <c r="K53" s="1">
+        <v>43.7</v>
+      </c>
+      <c r="L53" t="s">
+        <v>127</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>32</v>
+      </c>
+      <c r="B54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54">
+        <v>40.55</v>
+      </c>
+      <c r="G54" t="s">
+        <v>77</v>
+      </c>
+      <c r="H54">
+        <v>1.53</v>
+      </c>
+      <c r="I54" s="1">
+        <v>62.04</v>
+      </c>
+      <c r="J54">
+        <v>1.56</v>
+      </c>
+      <c r="K54" s="1">
+        <v>63.26</v>
+      </c>
+      <c r="L54" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="5" t="s">
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" t="s">
+        <v>76</v>
+      </c>
+      <c r="F55">
+        <v>11.83</v>
+      </c>
+      <c r="G55" t="s">
+        <v>77</v>
+      </c>
+      <c r="H55">
+        <v>1.72</v>
+      </c>
+      <c r="I55" s="1">
+        <v>20.35</v>
+      </c>
+      <c r="J55">
+        <v>1.75</v>
+      </c>
+      <c r="K55" s="1">
+        <v>20.7</v>
+      </c>
+      <c r="L55" t="s">
+        <v>128</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56">
+        <v>36.31</v>
+      </c>
+      <c r="G56" t="s">
+        <v>77</v>
+      </c>
+      <c r="H56">
+        <v>1.72</v>
+      </c>
+      <c r="I56" s="1">
+        <v>62.45</v>
+      </c>
+      <c r="J56">
+        <v>1.75</v>
+      </c>
+      <c r="K56" s="1">
+        <v>63.54</v>
+      </c>
+      <c r="L56" t="s">
+        <v>129</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57">
+        <v>21.85</v>
+      </c>
+      <c r="G57" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57">
+        <v>1.52</v>
+      </c>
+      <c r="I57" s="1">
+        <v>33.21</v>
+      </c>
+      <c r="J57">
+        <v>1.55</v>
+      </c>
+      <c r="K57" s="1">
+        <v>33.87</v>
+      </c>
+      <c r="L57" t="s">
+        <v>130</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" t="s">
+        <v>73</v>
+      </c>
+      <c r="F58">
+        <v>36.05</v>
+      </c>
+      <c r="G58" t="s">
+        <v>77</v>
+      </c>
+      <c r="H58">
+        <v>0.63</v>
+      </c>
+      <c r="I58" s="1">
+        <v>22.71</v>
+      </c>
+      <c r="J58">
+        <v>0.64</v>
+      </c>
+      <c r="K58" s="1">
+        <v>23.07</v>
+      </c>
+      <c r="L58" t="s">
+        <v>131</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>34</v>
+      </c>
+      <c r="B59" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="6">
-        <v>750.34</v>
-      </c>
-      <c r="C34" s="6">
-        <v>11</v>
-      </c>
-      <c r="D34" s="7">
-        <v>1.5062</v>
-      </c>
-      <c r="E34" s="6">
-        <v>1130.16</v>
-      </c>
-      <c r="F34" s="6">
-        <v>1152.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="6">
-        <v>408.62</v>
-      </c>
-      <c r="C35" s="6">
-        <v>13</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1.4646</v>
-      </c>
-      <c r="E35" s="6">
-        <v>598.48</v>
-      </c>
-      <c r="F35" s="6">
-        <v>610.74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5" t="s">
+      <c r="E59" t="s">
+        <v>76</v>
+      </c>
+      <c r="F59">
+        <v>145</v>
+      </c>
+      <c r="G59" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59">
+        <v>1.72</v>
+      </c>
+      <c r="I59" s="1">
+        <v>249.4</v>
+      </c>
+      <c r="J59">
+        <v>1.75</v>
+      </c>
+      <c r="K59" s="1">
+        <v>253.75</v>
+      </c>
+      <c r="L59" t="s">
+        <v>132</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>34</v>
+      </c>
+      <c r="B60" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" t="s">
+        <v>61</v>
+      </c>
+      <c r="E60" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>77</v>
+      </c>
+      <c r="H60">
+        <v>1.52</v>
+      </c>
+      <c r="I60" s="1">
+        <v>50.16</v>
+      </c>
+      <c r="J60">
+        <v>1.55</v>
+      </c>
+      <c r="K60" s="1">
+        <v>51.15</v>
+      </c>
+      <c r="L60" t="s">
+        <v>133</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" t="s">
+        <v>75</v>
+      </c>
+      <c r="F61">
+        <v>61.03</v>
+      </c>
+      <c r="G61" t="s">
+        <v>77</v>
+      </c>
+      <c r="H61">
+        <v>1.98</v>
+      </c>
+      <c r="I61" s="1">
+        <v>120.84</v>
+      </c>
+      <c r="J61">
+        <v>2.01</v>
+      </c>
+      <c r="K61" s="1">
+        <v>122.67</v>
+      </c>
+      <c r="L61" t="s">
+        <v>134</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" t="s">
+        <v>76</v>
+      </c>
+      <c r="F62">
+        <v>9.59</v>
+      </c>
+      <c r="G62" t="s">
+        <v>77</v>
+      </c>
+      <c r="H62">
+        <v>1.73</v>
+      </c>
+      <c r="I62" s="1">
+        <v>16.59</v>
+      </c>
+      <c r="J62">
+        <v>1.76</v>
+      </c>
+      <c r="K62" s="1">
+        <v>16.88</v>
+      </c>
+      <c r="L62" t="s">
+        <v>135</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63">
+        <v>39.56</v>
+      </c>
+      <c r="G63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63">
+        <v>1.52</v>
+      </c>
+      <c r="I63" s="1">
+        <v>60.13</v>
+      </c>
+      <c r="J63">
+        <v>1.55</v>
+      </c>
+      <c r="K63" s="1">
+        <v>61.32</v>
+      </c>
+      <c r="L63" t="s">
+        <v>136</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="6">
-        <v>128.83</v>
-      </c>
-      <c r="C36" s="6">
+      <c r="E64" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64">
+        <v>29.28</v>
+      </c>
+      <c r="G64" t="s">
+        <v>77</v>
+      </c>
+      <c r="H64">
+        <v>1.74</v>
+      </c>
+      <c r="I64" s="1">
+        <v>50.95</v>
+      </c>
+      <c r="J64">
+        <v>1.77</v>
+      </c>
+      <c r="K64" s="1">
+        <v>51.83</v>
+      </c>
+      <c r="L64" t="s">
+        <v>137</v>
+      </c>
+      <c r="M64">
+        <v>431740</v>
+      </c>
+      <c r="N64" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" t="s">
+        <v>36</v>
+      </c>
+      <c r="B65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" t="s">
+        <v>41</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" t="s">
+        <v>75</v>
+      </c>
+      <c r="F65">
+        <v>42.45</v>
+      </c>
+      <c r="G65" t="s">
+        <v>77</v>
+      </c>
+      <c r="H65">
         <v>2</v>
       </c>
-      <c r="D36" s="7">
-        <v>1.7448</v>
-      </c>
-      <c r="E36" s="6">
-        <v>224.78</v>
-      </c>
-      <c r="F36" s="6">
-        <v>228.65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="6">
-        <v>67.44</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2</v>
-      </c>
-      <c r="D37" s="7">
-        <v>0.6332</v>
-      </c>
-      <c r="E37" s="6">
-        <v>42.7</v>
-      </c>
-      <c r="F37" s="6">
-        <v>43.37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="9">
-        <v>1355.23</v>
-      </c>
-      <c r="C38" s="9">
-        <v>28</v>
-      </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="9">
-        <v>1996.12</v>
-      </c>
-      <c r="F38" s="9">
-        <v>2035.41</v>
+      <c r="I65" s="1">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="J65">
+        <v>2.03</v>
+      </c>
+      <c r="K65" s="1">
+        <v>86.17</v>
+      </c>
+      <c r="L65" t="s">
+        <v>138</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="6">
+        <v>1534.71</v>
+      </c>
+      <c r="C70" s="6">
+        <v>24</v>
+      </c>
+      <c r="D70" s="7">
+        <v>1.5939</v>
+      </c>
+      <c r="E70" s="6">
+        <v>2446.14</v>
+      </c>
+      <c r="F70" s="6">
+        <v>2492.17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="6">
+        <v>850.53</v>
+      </c>
+      <c r="C71" s="6">
+        <v>29</v>
+      </c>
+      <c r="D71" s="7">
+        <v>1.4867</v>
+      </c>
+      <c r="E71" s="6">
+        <v>1264.45</v>
+      </c>
+      <c r="F71" s="6">
+        <v>1289.96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="6">
+        <v>351.65</v>
+      </c>
+      <c r="C72" s="6">
+        <v>6</v>
+      </c>
+      <c r="D72" s="7">
+        <v>1.8684</v>
+      </c>
+      <c r="E72" s="6">
+        <v>657.02</v>
+      </c>
+      <c r="F72" s="6">
+        <v>667.5700000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="6">
+        <v>172.56</v>
+      </c>
+      <c r="C73" s="6">
+        <v>5</v>
+      </c>
+      <c r="D73" s="7">
+        <v>0.6313</v>
+      </c>
+      <c r="E73" s="6">
+        <v>108.93</v>
+      </c>
+      <c r="F73" s="6">
+        <v>110.65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B74" s="9">
+        <v>2909.45</v>
+      </c>
+      <c r="C74" s="9">
+        <v>64</v>
+      </c>
+      <c r="D74" s="7"/>
+      <c r="E74" s="9">
+        <v>4476.54</v>
+      </c>
+      <c r="F74" s="9">
+        <v>4560.35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A68:F68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -649,7 +649,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3960,7 +3960,7 @@
         <v>24</v>
       </c>
       <c r="D70" s="7">
-        <v>1.5939</v>
+        <v>1.593878</v>
       </c>
       <c r="E70" s="6">
         <v>2446.14</v>
@@ -3980,7 +3980,7 @@
         <v>29</v>
       </c>
       <c r="D71" s="7">
-        <v>1.4867</v>
+        <v>1.486661</v>
       </c>
       <c r="E71" s="6">
         <v>1264.45</v>
@@ -4000,7 +4000,7 @@
         <v>6</v>
       </c>
       <c r="D72" s="7">
-        <v>1.8684</v>
+        <v>1.868392</v>
       </c>
       <c r="E72" s="6">
         <v>657.02</v>
@@ -4020,7 +4020,7 @@
         <v>5</v>
       </c>
       <c r="D73" s="7">
-        <v>0.6313</v>
+        <v>0.631259</v>
       </c>
       <c r="E73" s="6">
         <v>108.93</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="209">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -651,8 +648,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -745,10 +742,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1043,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1056,13 +1053,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1105,3021 +1102,2826 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2">
         <v>29.5</v>
       </c>
       <c r="G2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2">
+        <v>0.65</v>
+      </c>
+      <c r="I2" s="1">
+        <v>19.175</v>
+      </c>
+      <c r="J2">
+        <v>0.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>19.47</v>
+      </c>
+      <c r="L2" t="s">
         <v>78</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>19.175</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L2" s="1">
-        <v>19.47</v>
-      </c>
-      <c r="M2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3">
         <v>23.973</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.47</v>
       </c>
       <c r="I3" s="1">
-        <v>1.47</v>
+        <v>35.24</v>
       </c>
       <c r="J3">
-        <v>35.24031</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
-        <v>35.9595</v>
-      </c>
-      <c r="M3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>35.96</v>
+      </c>
+      <c r="L3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4">
         <v>67.542</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4">
-        <v>1.619</v>
+        <v>1.74</v>
       </c>
       <c r="I4" s="1">
-        <v>1.74</v>
+        <v>117.523</v>
       </c>
       <c r="J4">
-        <v>117.52308</v>
+        <v>1.77</v>
       </c>
       <c r="K4" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L4" s="1">
-        <v>119.54934</v>
-      </c>
-      <c r="M4" t="s">
-        <v>81</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>119.549</v>
+      </c>
+      <c r="L4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5">
         <v>44.199</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5">
-        <v>1.399</v>
+        <v>1.48</v>
       </c>
       <c r="I5" s="1">
-        <v>1.48</v>
+        <v>65.41500000000001</v>
       </c>
       <c r="J5">
-        <v>65.41452</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>66.74048999999999</v>
-      </c>
-      <c r="M5" t="s">
-        <v>82</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F6">
         <v>26.49</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6">
-        <v>1.399</v>
+        <v>1.48</v>
       </c>
       <c r="I6" s="1">
-        <v>1.48</v>
+        <v>39.205</v>
       </c>
       <c r="J6">
-        <v>39.2052</v>
+        <v>1.51</v>
       </c>
       <c r="K6" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L6" s="1">
-        <v>39.9999</v>
-      </c>
-      <c r="M6" t="s">
-        <v>83</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7">
         <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7">
-        <v>1.359</v>
+        <v>1.47</v>
       </c>
       <c r="I7" s="1">
-        <v>1.47</v>
+        <v>45.57</v>
       </c>
       <c r="J7">
-        <v>45.57</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L7" s="1">
         <v>46.5</v>
       </c>
-      <c r="M7" t="s">
-        <v>84</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" t="s">
+        <v>83</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F8">
         <v>116</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8">
-        <v>1.399</v>
+        <v>1.48</v>
       </c>
       <c r="I8" s="1">
-        <v>1.48</v>
+        <v>171.68</v>
       </c>
       <c r="J8">
-        <v>171.68</v>
+        <v>1.51</v>
       </c>
       <c r="K8" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L8" s="1">
         <v>175.16</v>
       </c>
-      <c r="M8" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="L8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9">
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9">
-        <v>1.359</v>
+        <v>1.47</v>
       </c>
       <c r="I9" s="1">
-        <v>1.47</v>
+        <v>44.1</v>
       </c>
       <c r="J9">
-        <v>44.1</v>
+        <v>1.5</v>
       </c>
       <c r="K9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L9" s="1">
         <v>45</v>
       </c>
-      <c r="M9" t="s">
-        <v>86</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="L9" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10">
         <v>61.292</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10">
-        <v>1.599</v>
+        <v>1.75</v>
       </c>
       <c r="I10" s="1">
-        <v>1.75</v>
+        <v>107.261</v>
       </c>
       <c r="J10">
-        <v>107.261</v>
+        <v>1.78</v>
       </c>
       <c r="K10" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L10" s="1">
-        <v>109.09976</v>
-      </c>
-      <c r="M10" t="s">
-        <v>87</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>109.1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11">
         <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11">
-        <v>1.406</v>
+        <v>1.49</v>
       </c>
       <c r="I11" s="1">
-        <v>1.49</v>
+        <v>38.74</v>
       </c>
       <c r="J11">
-        <v>38.74</v>
+        <v>1.52</v>
       </c>
       <c r="K11" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L11" s="1">
         <v>39.52</v>
       </c>
-      <c r="M11" t="s">
-        <v>88</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12">
         <v>56.217</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12">
-        <v>1.406</v>
+        <v>1.49</v>
       </c>
       <c r="I12" s="1">
-        <v>1.49</v>
+        <v>83.76300000000001</v>
       </c>
       <c r="J12">
-        <v>83.76333</v>
+        <v>1.52</v>
       </c>
       <c r="K12" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L12" s="1">
-        <v>85.44983999999999</v>
-      </c>
-      <c r="M12" t="s">
-        <v>89</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>85.45</v>
+      </c>
+      <c r="L12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F13">
         <v>21.94</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13">
-        <v>1.359</v>
+        <v>1.47</v>
       </c>
       <c r="I13" s="1">
-        <v>1.47</v>
+        <v>32.252</v>
       </c>
       <c r="J13">
-        <v>32.2518</v>
+        <v>1.5</v>
       </c>
       <c r="K13" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L13" s="1">
         <v>32.91</v>
       </c>
-      <c r="M13" t="s">
-        <v>90</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="L13" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F14">
         <v>47.953</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H14">
-        <v>1.359</v>
+        <v>1.47</v>
       </c>
       <c r="I14" s="1">
-        <v>1.47</v>
+        <v>70.491</v>
       </c>
       <c r="J14">
-        <v>70.49091</v>
+        <v>1.5</v>
       </c>
       <c r="K14" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L14" s="1">
-        <v>71.9295</v>
-      </c>
-      <c r="M14" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F15">
         <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15">
-        <v>1.359</v>
+        <v>1.47</v>
       </c>
       <c r="I15" s="1">
-        <v>1.47</v>
+        <v>49.98</v>
       </c>
       <c r="J15">
-        <v>49.98</v>
+        <v>1.5</v>
       </c>
       <c r="K15" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L15" s="1">
         <v>51</v>
       </c>
-      <c r="M15" t="s">
-        <v>92</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="L15" t="s">
+        <v>91</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F16">
         <v>41.45</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I16" s="1">
-        <v>1.46</v>
+        <v>60.517</v>
       </c>
       <c r="J16">
-        <v>60.517</v>
+        <v>1.49</v>
       </c>
       <c r="K16" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L16" s="1">
-        <v>61.7605</v>
-      </c>
-      <c r="M16" t="s">
-        <v>93</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>61.76</v>
+      </c>
+      <c r="L16" t="s">
+        <v>92</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17">
         <v>146</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H17">
-        <v>1.412</v>
+        <v>1.49</v>
       </c>
       <c r="I17" s="1">
-        <v>1.49</v>
+        <v>217.54</v>
       </c>
       <c r="J17">
-        <v>217.54</v>
+        <v>1.52</v>
       </c>
       <c r="K17" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L17" s="1">
         <v>221.92</v>
       </c>
-      <c r="M17" t="s">
-        <v>94</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="L17" t="s">
+        <v>93</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18">
         <v>37.937</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I18" s="1">
-        <v>0.62</v>
+        <v>23.521</v>
       </c>
       <c r="J18">
-        <v>23.52094</v>
+        <v>0.63</v>
       </c>
       <c r="K18" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L18" s="1">
-        <v>23.90031</v>
-      </c>
-      <c r="M18" t="s">
-        <v>95</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>23.9</v>
+      </c>
+      <c r="L18" t="s">
+        <v>94</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F19">
         <v>32.351</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H19">
-        <v>1.437</v>
+        <v>1.51</v>
       </c>
       <c r="I19" s="1">
-        <v>1.51</v>
+        <v>48.85</v>
       </c>
       <c r="J19">
-        <v>48.85001</v>
+        <v>1.54</v>
       </c>
       <c r="K19" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L19" s="1">
-        <v>49.82054</v>
-      </c>
-      <c r="M19" t="s">
-        <v>96</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>49.821</v>
+      </c>
+      <c r="L19" t="s">
+        <v>95</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F20">
         <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I20" s="1">
-        <v>1.46</v>
+        <v>45.26</v>
       </c>
       <c r="J20">
-        <v>45.26</v>
+        <v>1.49</v>
       </c>
       <c r="K20" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L20" s="1">
         <v>46.19</v>
       </c>
-      <c r="M20" t="s">
-        <v>97</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="L20" t="s">
+        <v>96</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F21">
         <v>18.027</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I21" s="1">
-        <v>1.46</v>
+        <v>26.319</v>
       </c>
       <c r="J21">
-        <v>26.31942</v>
+        <v>1.49</v>
       </c>
       <c r="K21" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L21" s="1">
-        <v>26.86023</v>
-      </c>
-      <c r="M21" t="s">
-        <v>98</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>26.86</v>
+      </c>
+      <c r="L21" t="s">
+        <v>97</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F22">
         <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22">
-        <v>1.451</v>
+        <v>1.53</v>
       </c>
       <c r="I22" s="1">
-        <v>1.53</v>
+        <v>218.79</v>
       </c>
       <c r="J22">
-        <v>218.79</v>
+        <v>1.56</v>
       </c>
       <c r="K22" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L22" s="1">
         <v>223.08</v>
       </c>
-      <c r="M22" t="s">
-        <v>99</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="L22" t="s">
+        <v>98</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23">
         <v>39.463</v>
       </c>
       <c r="G23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23">
-        <v>1.359</v>
+        <v>1.46</v>
       </c>
       <c r="I23" s="1">
-        <v>1.46</v>
+        <v>57.616</v>
       </c>
       <c r="J23">
-        <v>57.61598</v>
+        <v>1.49</v>
       </c>
       <c r="K23" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L23" s="1">
-        <v>58.79987</v>
-      </c>
-      <c r="M23" t="s">
-        <v>100</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>58.8</v>
+      </c>
+      <c r="L23" t="s">
+        <v>99</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F24">
         <v>33.84</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24">
-        <v>1.451</v>
+        <v>1.53</v>
       </c>
       <c r="I24" s="1">
-        <v>1.53</v>
+        <v>51.775</v>
       </c>
       <c r="J24">
-        <v>51.7752</v>
+        <v>1.56</v>
       </c>
       <c r="K24" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L24" s="1">
-        <v>52.7904</v>
-      </c>
-      <c r="M24" t="s">
-        <v>101</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>52.79</v>
+      </c>
+      <c r="L24" t="s">
+        <v>100</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25">
         <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25">
-        <v>1.369</v>
+        <v>1.46</v>
       </c>
       <c r="I25" s="1">
-        <v>1.46</v>
+        <v>33.58</v>
       </c>
       <c r="J25">
-        <v>33.58</v>
+        <v>1.49</v>
       </c>
       <c r="K25" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L25" s="1">
         <v>34.27</v>
       </c>
-      <c r="M25" t="s">
-        <v>102</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="L25" t="s">
+        <v>101</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26">
         <v>40.819</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H26">
-        <v>1.369</v>
+        <v>1.46</v>
       </c>
       <c r="I26" s="1">
-        <v>1.46</v>
+        <v>59.596</v>
       </c>
       <c r="J26">
-        <v>59.59574</v>
+        <v>1.49</v>
       </c>
       <c r="K26" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L26" s="1">
-        <v>60.82031</v>
-      </c>
-      <c r="M26" t="s">
-        <v>84</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>60.82</v>
+      </c>
+      <c r="L26" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F27">
         <v>64.288</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27">
-        <v>1.469</v>
+        <v>1.53</v>
       </c>
       <c r="I27" s="1">
-        <v>1.53</v>
+        <v>98.361</v>
       </c>
       <c r="J27">
-        <v>98.36064</v>
+        <v>1.56</v>
       </c>
       <c r="K27" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L27" s="1">
-        <v>100.28928</v>
-      </c>
-      <c r="M27" t="s">
-        <v>103</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>100.289</v>
+      </c>
+      <c r="L27" t="s">
+        <v>102</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F28">
         <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H28">
-        <v>1.369</v>
+        <v>1.46</v>
       </c>
       <c r="I28" s="1">
-        <v>1.46</v>
+        <v>37.96</v>
       </c>
       <c r="J28">
-        <v>37.96</v>
+        <v>1.49</v>
       </c>
       <c r="K28" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L28" s="1">
         <v>38.74</v>
       </c>
-      <c r="M28" t="s">
-        <v>97</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="L28" t="s">
+        <v>96</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F29">
         <v>61.949</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29">
-        <v>1.489</v>
+        <v>1.55</v>
       </c>
       <c r="I29" s="1">
-        <v>1.55</v>
+        <v>96.021</v>
       </c>
       <c r="J29">
-        <v>96.02095</v>
+        <v>1.58</v>
       </c>
       <c r="K29" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L29" s="1">
-        <v>97.87942</v>
-      </c>
-      <c r="M29" t="s">
-        <v>104</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+        <v>97.879</v>
+      </c>
+      <c r="L29" t="s">
+        <v>103</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F30">
         <v>19.993</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30">
-        <v>1.369</v>
+        <v>1.47</v>
       </c>
       <c r="I30" s="1">
-        <v>1.47</v>
+        <v>29.39</v>
       </c>
       <c r="J30">
-        <v>29.38971</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L30" s="1">
-        <v>29.9895</v>
-      </c>
-      <c r="M30" t="s">
-        <v>105</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>29.99</v>
+      </c>
+      <c r="L30" t="s">
+        <v>104</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F31">
         <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I31" s="1">
-        <v>1.58</v>
+        <v>52.14</v>
       </c>
       <c r="J31">
-        <v>52.14</v>
+        <v>1.61</v>
       </c>
       <c r="K31" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L31" s="1">
         <v>53.13</v>
       </c>
-      <c r="M31" t="s">
-        <v>106</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="L31" t="s">
+        <v>105</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F32">
         <v>16.46</v>
       </c>
       <c r="G32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H32">
-        <v>1.369</v>
+        <v>1.47</v>
       </c>
       <c r="I32" s="1">
-        <v>1.47</v>
+        <v>24.196</v>
       </c>
       <c r="J32">
-        <v>24.1962</v>
+        <v>1.5</v>
       </c>
       <c r="K32" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L32" s="1">
         <v>24.69</v>
       </c>
-      <c r="M32" t="s">
-        <v>107</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="L32" t="s">
+        <v>106</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F33">
         <v>31.713</v>
       </c>
       <c r="G33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H33">
-        <v>1.369</v>
+        <v>1.47</v>
       </c>
       <c r="I33" s="1">
-        <v>1.47</v>
+        <v>46.618</v>
       </c>
       <c r="J33">
-        <v>46.61811</v>
+        <v>1.5</v>
       </c>
       <c r="K33" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L33" s="1">
-        <v>47.5695</v>
-      </c>
-      <c r="M33" t="s">
-        <v>108</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>47.57</v>
+      </c>
+      <c r="L33" t="s">
+        <v>107</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F34">
         <v>54.619</v>
       </c>
       <c r="G34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H34">
-        <v>1.599</v>
+        <v>1.86</v>
       </c>
       <c r="I34" s="1">
-        <v>1.86</v>
+        <v>101.591</v>
       </c>
       <c r="J34">
-        <v>101.59134</v>
+        <v>1.89</v>
       </c>
       <c r="K34" s="1">
-        <v>1.89</v>
-      </c>
-      <c r="L34" s="1">
-        <v>103.22991</v>
-      </c>
-      <c r="M34" t="s">
-        <v>109</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>103.23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>108</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F35">
         <v>31.589</v>
       </c>
       <c r="G35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H35">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I35" s="1">
-        <v>1.6</v>
+        <v>50.542</v>
       </c>
       <c r="J35">
-        <v>50.5424</v>
+        <v>1.63</v>
       </c>
       <c r="K35" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L35" s="1">
-        <v>51.49007</v>
-      </c>
-      <c r="M35" t="s">
-        <v>110</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+        <v>51.49</v>
+      </c>
+      <c r="L35" t="s">
+        <v>109</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F36">
         <v>41.125</v>
       </c>
       <c r="G36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I36" s="1">
-        <v>0.63</v>
+        <v>25.909</v>
       </c>
       <c r="J36">
-        <v>25.90875</v>
+        <v>0.64</v>
       </c>
       <c r="K36" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L36" s="1">
         <v>26.32</v>
       </c>
-      <c r="M36" t="s">
-        <v>111</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="L36" t="s">
+        <v>110</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F37">
         <v>19.307</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H37">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I37" s="1">
-        <v>1.5</v>
+        <v>28.96</v>
       </c>
       <c r="J37">
-        <v>28.9605</v>
+        <v>1.53</v>
       </c>
       <c r="K37" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L37" s="1">
-        <v>29.53971</v>
-      </c>
-      <c r="M37" t="s">
-        <v>112</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>29.54</v>
+      </c>
+      <c r="L37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F38">
         <v>170.988</v>
       </c>
       <c r="G38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H38">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I38" s="1">
-        <v>1.65</v>
+        <v>282.13</v>
       </c>
       <c r="J38">
-        <v>282.1302</v>
+        <v>1.68</v>
       </c>
       <c r="K38" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L38" s="1">
-        <v>287.25984</v>
-      </c>
-      <c r="M38" t="s">
-        <v>113</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>287.26</v>
+      </c>
+      <c r="L38" t="s">
+        <v>112</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F39">
         <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H39">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I39" s="1">
-        <v>1.5</v>
+        <v>46.5</v>
       </c>
       <c r="J39">
-        <v>46.5</v>
+        <v>1.53</v>
       </c>
       <c r="K39" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L39" s="1">
         <v>47.43</v>
       </c>
-      <c r="M39" t="s">
-        <v>114</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="L39" t="s">
+        <v>113</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F40">
         <v>66.262</v>
       </c>
       <c r="G40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H40">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I40" s="1">
-        <v>1.65</v>
+        <v>109.332</v>
       </c>
       <c r="J40">
-        <v>109.3323</v>
+        <v>1.68</v>
       </c>
       <c r="K40" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L40" s="1">
-        <v>111.32016</v>
-      </c>
-      <c r="M40" t="s">
-        <v>115</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+        <v>111.32</v>
+      </c>
+      <c r="L40" t="s">
+        <v>114</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F41">
         <v>40.438</v>
       </c>
       <c r="G41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H41">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I41" s="1">
-        <v>1.5</v>
+        <v>60.657</v>
       </c>
       <c r="J41">
-        <v>60.657</v>
+        <v>1.53</v>
       </c>
       <c r="K41" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L41" s="1">
-        <v>61.87014</v>
-      </c>
-      <c r="M41" t="s">
-        <v>116</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>61.87</v>
+      </c>
+      <c r="L41" t="s">
+        <v>115</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F42">
         <v>24.799</v>
       </c>
       <c r="G42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H42">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I42" s="1">
-        <v>1.51</v>
+        <v>37.446</v>
       </c>
       <c r="J42">
-        <v>37.44649</v>
+        <v>1.54</v>
       </c>
       <c r="K42" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L42" s="1">
-        <v>38.19046</v>
-      </c>
-      <c r="M42" t="s">
-        <v>117</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>38.19</v>
+      </c>
+      <c r="L42" t="s">
+        <v>116</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F43">
         <v>21.812</v>
       </c>
       <c r="G43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H43">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I43" s="1">
-        <v>1.51</v>
+        <v>32.936</v>
       </c>
       <c r="J43">
-        <v>32.93612</v>
+        <v>1.54</v>
       </c>
       <c r="K43" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L43" s="1">
-        <v>33.59048</v>
-      </c>
-      <c r="M43" t="s">
-        <v>118</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>33.59</v>
+      </c>
+      <c r="L43" t="s">
+        <v>117</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F44">
         <v>31.911</v>
       </c>
       <c r="G44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H44">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I44" s="1">
-        <v>1.66</v>
+        <v>52.972</v>
       </c>
       <c r="J44">
-        <v>52.97226</v>
+        <v>1.69</v>
       </c>
       <c r="K44" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L44" s="1">
-        <v>53.92959</v>
-      </c>
-      <c r="M44" t="s">
-        <v>119</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+        <v>53.93</v>
+      </c>
+      <c r="L44" t="s">
+        <v>118</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F45">
         <v>15.688</v>
       </c>
       <c r="G45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H45">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I45" s="1">
-        <v>1.67</v>
+        <v>26.199</v>
       </c>
       <c r="J45">
-        <v>26.19896</v>
+        <v>1.7</v>
       </c>
       <c r="K45" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L45" s="1">
-        <v>26.6696</v>
-      </c>
-      <c r="M45" t="s">
-        <v>120</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+        <v>26.67</v>
+      </c>
+      <c r="L45" t="s">
+        <v>119</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F46">
         <v>64.71899999999999</v>
       </c>
       <c r="G46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H46">
-        <v>1.648</v>
+        <v>1.93</v>
       </c>
       <c r="I46" s="1">
-        <v>1.93</v>
+        <v>124.908</v>
       </c>
       <c r="J46">
-        <v>124.90767</v>
+        <v>1.96</v>
       </c>
       <c r="K46" s="1">
-        <v>1.96</v>
-      </c>
-      <c r="L46" s="1">
-        <v>126.84924</v>
-      </c>
-      <c r="M46" t="s">
-        <v>121</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+        <v>126.849</v>
+      </c>
+      <c r="L46" t="s">
+        <v>120</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F47">
         <v>13</v>
       </c>
       <c r="G47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H47">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I47" s="1">
-        <v>1.51</v>
+        <v>19.63</v>
       </c>
       <c r="J47">
-        <v>19.63</v>
+        <v>1.54</v>
       </c>
       <c r="K47" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L47" s="1">
         <v>20.02</v>
       </c>
-      <c r="M47" t="s">
-        <v>122</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="L47" t="s">
+        <v>121</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F48">
         <v>31.091</v>
       </c>
       <c r="G48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H48">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I48" s="1">
-        <v>1.51</v>
+        <v>46.947</v>
       </c>
       <c r="J48">
-        <v>46.94741</v>
+        <v>1.54</v>
       </c>
       <c r="K48" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L48" s="1">
-        <v>47.88014</v>
-      </c>
-      <c r="M48" t="s">
-        <v>123</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <v>47.88</v>
+      </c>
+      <c r="L48" t="s">
+        <v>122</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F49">
         <v>27.953</v>
       </c>
       <c r="G49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I49" s="1">
-        <v>0.63</v>
+        <v>17.61</v>
       </c>
       <c r="J49">
-        <v>17.61039</v>
+        <v>0.64</v>
       </c>
       <c r="K49" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L49" s="1">
-        <v>17.88992</v>
-      </c>
-      <c r="M49" t="s">
-        <v>124</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+        <v>17.89</v>
+      </c>
+      <c r="L49" t="s">
+        <v>123</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F50">
         <v>68.93000000000001</v>
       </c>
       <c r="G50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H50">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I50" s="1">
-        <v>1.69</v>
+        <v>116.492</v>
       </c>
       <c r="J50">
-        <v>116.4917</v>
+        <v>1.72</v>
       </c>
       <c r="K50" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L50" s="1">
-        <v>118.5596</v>
-      </c>
-      <c r="M50" t="s">
-        <v>125</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+        <v>118.56</v>
+      </c>
+      <c r="L50" t="s">
+        <v>124</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F51">
         <v>29.331</v>
       </c>
       <c r="G51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H51">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I51" s="1">
-        <v>1.51</v>
+        <v>44.29</v>
       </c>
       <c r="J51">
-        <v>44.28981</v>
+        <v>1.54</v>
       </c>
       <c r="K51" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L51" s="1">
-        <v>45.16974</v>
-      </c>
-      <c r="M51" t="s">
-        <v>126</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>45.17</v>
+      </c>
+      <c r="L51" t="s">
+        <v>125</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F52">
         <v>133.988</v>
       </c>
       <c r="G52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H52">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I52" s="1">
-        <v>1.69</v>
+        <v>226.44</v>
       </c>
       <c r="J52">
-        <v>226.43972</v>
+        <v>1.72</v>
       </c>
       <c r="K52" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L52" s="1">
-        <v>230.45936</v>
-      </c>
-      <c r="M52" t="s">
-        <v>127</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>230.459</v>
+      </c>
+      <c r="L52" t="s">
+        <v>126</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F53">
         <v>28.013</v>
       </c>
       <c r="G53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H53">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I53" s="1">
-        <v>1.53</v>
+        <v>42.86</v>
       </c>
       <c r="J53">
-        <v>42.85989</v>
+        <v>1.56</v>
       </c>
       <c r="K53" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L53" s="1">
-        <v>43.70028</v>
-      </c>
-      <c r="M53" t="s">
-        <v>128</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>43.7</v>
+      </c>
+      <c r="L53" t="s">
+        <v>127</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F54">
         <v>40.551</v>
       </c>
       <c r="G54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H54">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I54" s="1">
-        <v>1.53</v>
+        <v>62.043</v>
       </c>
       <c r="J54">
-        <v>62.04303</v>
+        <v>1.56</v>
       </c>
       <c r="K54" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L54" s="1">
-        <v>63.25956</v>
-      </c>
-      <c r="M54" t="s">
-        <v>92</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+        <v>63.26</v>
+      </c>
+      <c r="L54" t="s">
+        <v>91</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F55">
         <v>11.829</v>
       </c>
       <c r="G55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H55">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I55" s="1">
-        <v>1.72</v>
+        <v>20.346</v>
       </c>
       <c r="J55">
-        <v>20.34588</v>
+        <v>1.75</v>
       </c>
       <c r="K55" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L55" s="1">
-        <v>20.70075</v>
-      </c>
-      <c r="M55" t="s">
-        <v>129</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>20.701</v>
+      </c>
+      <c r="L55" t="s">
+        <v>128</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E56" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F56">
         <v>36.309</v>
       </c>
       <c r="G56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H56">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I56" s="1">
-        <v>1.72</v>
+        <v>62.451</v>
       </c>
       <c r="J56">
-        <v>62.45148</v>
+        <v>1.75</v>
       </c>
       <c r="K56" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L56" s="1">
-        <v>63.54075</v>
-      </c>
-      <c r="M56" t="s">
-        <v>130</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+        <v>63.541</v>
+      </c>
+      <c r="L56" t="s">
+        <v>129</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F57">
         <v>21.852</v>
       </c>
       <c r="G57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H57">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I57" s="1">
-        <v>1.52</v>
+        <v>33.215</v>
       </c>
       <c r="J57">
-        <v>33.21504</v>
+        <v>1.55</v>
       </c>
       <c r="K57" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L57" s="1">
-        <v>33.8706</v>
-      </c>
-      <c r="M57" t="s">
-        <v>131</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+        <v>33.871</v>
+      </c>
+      <c r="L57" t="s">
+        <v>130</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F58">
         <v>36.047</v>
       </c>
       <c r="G58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I58" s="1">
-        <v>0.63</v>
+        <v>22.71</v>
       </c>
       <c r="J58">
-        <v>22.70961</v>
+        <v>0.64</v>
       </c>
       <c r="K58" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L58" s="1">
-        <v>23.07008</v>
-      </c>
-      <c r="M58" t="s">
-        <v>132</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>23.07</v>
+      </c>
+      <c r="L58" t="s">
+        <v>131</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F59">
         <v>145</v>
       </c>
       <c r="G59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H59">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I59" s="1">
-        <v>1.72</v>
+        <v>249.4</v>
       </c>
       <c r="J59">
-        <v>249.4</v>
+        <v>1.75</v>
       </c>
       <c r="K59" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L59" s="1">
         <v>253.75</v>
       </c>
-      <c r="M59" t="s">
-        <v>133</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="L59" t="s">
+        <v>132</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E60" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F60">
         <v>33</v>
       </c>
       <c r="G60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H60">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I60" s="1">
-        <v>1.52</v>
+        <v>50.16</v>
       </c>
       <c r="J60">
-        <v>50.16</v>
+        <v>1.55</v>
       </c>
       <c r="K60" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L60" s="1">
         <v>51.15</v>
       </c>
-      <c r="M60" t="s">
-        <v>134</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="L60" t="s">
+        <v>133</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F61">
         <v>61.03</v>
       </c>
       <c r="G61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H61">
-        <v>1.716</v>
+        <v>1.98</v>
       </c>
       <c r="I61" s="1">
-        <v>1.98</v>
+        <v>120.839</v>
       </c>
       <c r="J61">
-        <v>120.8394</v>
+        <v>2.01</v>
       </c>
       <c r="K61" s="1">
-        <v>2.01</v>
-      </c>
-      <c r="L61" s="1">
-        <v>122.6703</v>
-      </c>
-      <c r="M61" t="s">
-        <v>135</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+        <v>122.67</v>
+      </c>
+      <c r="L61" t="s">
+        <v>134</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F62">
         <v>9.590999999999999</v>
       </c>
       <c r="G62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H62">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I62" s="1">
-        <v>1.73</v>
+        <v>16.592</v>
       </c>
       <c r="J62">
-        <v>16.59243</v>
+        <v>1.76</v>
       </c>
       <c r="K62" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L62" s="1">
-        <v>16.88016</v>
-      </c>
-      <c r="M62" t="s">
-        <v>136</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>16.88</v>
+      </c>
+      <c r="L62" t="s">
+        <v>135</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F63">
         <v>39.561</v>
       </c>
       <c r="G63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H63">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I63" s="1">
-        <v>1.52</v>
+        <v>60.133</v>
       </c>
       <c r="J63">
-        <v>60.13272</v>
+        <v>1.55</v>
       </c>
       <c r="K63" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L63" s="1">
-        <v>61.31955</v>
-      </c>
-      <c r="M63" t="s">
-        <v>137</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+        <v>61.32</v>
+      </c>
+      <c r="L63" t="s">
+        <v>136</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F64">
         <v>29.282</v>
       </c>
       <c r="G64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H64">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I64" s="1">
-        <v>1.74</v>
+        <v>50.951</v>
       </c>
       <c r="J64">
-        <v>50.95068</v>
+        <v>1.77</v>
       </c>
       <c r="K64" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L64" s="1">
-        <v>51.82914</v>
-      </c>
-      <c r="M64" t="s">
-        <v>138</v>
-      </c>
-      <c r="N64">
+        <v>51.829</v>
+      </c>
+      <c r="L64" t="s">
+        <v>137</v>
+      </c>
+      <c r="M64">
         <v>431740</v>
       </c>
-      <c r="O64" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="N64" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F65">
         <v>42.448</v>
       </c>
       <c r="G65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H65">
-        <v>1.736</v>
+        <v>2</v>
       </c>
       <c r="I65" s="1">
-        <v>2</v>
+        <v>84.896</v>
       </c>
       <c r="J65">
-        <v>84.896</v>
+        <v>2.03</v>
       </c>
       <c r="K65" s="1">
-        <v>2.03</v>
-      </c>
-      <c r="L65" s="1">
-        <v>86.16943999999999</v>
-      </c>
-      <c r="M65" t="s">
-        <v>139</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65" t="s">
+        <v>86.169</v>
+      </c>
+      <c r="L65" t="s">
+        <v>138</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="3" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
-      <c r="A68" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -4127,109 +3929,109 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:14">
       <c r="A69" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="C69" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="D69" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>208</v>
-      </c>
       <c r="E69" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" s="6">
         <v>1534.701</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="7">
         <v>24</v>
       </c>
       <c r="D70" s="7">
-        <v>1.593879</v>
-      </c>
-      <c r="E70" s="6">
-        <v>2446.13</v>
-      </c>
-      <c r="F70" s="6">
-        <v>2492.17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+        <v>1.594</v>
+      </c>
+      <c r="E70" s="7">
+        <v>2446.127</v>
+      </c>
+      <c r="F70" s="7">
+        <v>2492.169</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B71" s="6">
         <v>850.546</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="7">
         <v>29</v>
       </c>
       <c r="D71" s="7">
-        <v>1.486649</v>
-      </c>
-      <c r="E71" s="6">
-        <v>1264.46</v>
-      </c>
-      <c r="F71" s="6">
-        <v>1289.98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15">
+        <v>1.487</v>
+      </c>
+      <c r="E71" s="7">
+        <v>1264.462</v>
+      </c>
+      <c r="F71" s="7">
+        <v>1289.981</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" s="6">
         <v>351.65</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="7">
         <v>6</v>
       </c>
       <c r="D72" s="7">
-        <v>1.868388</v>
-      </c>
-      <c r="E72" s="6">
-        <v>657.02</v>
-      </c>
-      <c r="F72" s="6">
-        <v>667.5700000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15">
+        <v>1.868</v>
+      </c>
+      <c r="E72" s="7">
+        <v>657.018</v>
+      </c>
+      <c r="F72" s="7">
+        <v>667.567</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B73" s="6">
         <v>172.562</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="7">
         <v>5</v>
       </c>
       <c r="D73" s="7">
-        <v>0.631221</v>
-      </c>
-      <c r="E73" s="6">
-        <v>108.92</v>
-      </c>
-      <c r="F73" s="6">
+        <v>0.631</v>
+      </c>
+      <c r="E73" s="7">
+        <v>108.925</v>
+      </c>
+      <c r="F73" s="7">
         <v>110.65</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:14">
       <c r="A74" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B74" s="9">
         <v>2909.459</v>
@@ -4239,10 +4041,10 @@
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="9">
-        <v>4476.53</v>
+        <v>4476.532</v>
       </c>
       <c r="F74" s="9">
-        <v>4560.37</v>
+        <v>4560.367</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА АКСАКОВО % 1/ОБЩИНА АКСАКОВО % 1.xlsx
@@ -1039,10 +1039,10 @@
         <v>78</v>
       </c>
       <c r="H2" s="1">
-        <v>1.669</v>
+        <v>1.76</v>
       </c>
       <c r="I2" s="1">
-        <v>101.675</v>
+        <v>107.219</v>
       </c>
       <c r="J2" s="1">
         <v>1.79</v>
@@ -1083,10 +1083,10 @@
         <v>78</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I3" s="1">
-        <v>30.009</v>
+        <v>31.92</v>
       </c>
       <c r="J3" s="1">
         <v>1.55</v>
@@ -1127,10 +1127,10 @@
         <v>78</v>
       </c>
       <c r="H4" s="1">
-        <v>1.746</v>
+        <v>2.02</v>
       </c>
       <c r="I4" s="1">
-        <v>94.494</v>
+        <v>109.322</v>
       </c>
       <c r="J4" s="1">
         <v>2.05</v>
@@ -1171,10 +1171,10 @@
         <v>78</v>
       </c>
       <c r="H5" s="1">
-        <v>1.669</v>
+        <v>1.76</v>
       </c>
       <c r="I5" s="1">
-        <v>107.116</v>
+        <v>112.957</v>
       </c>
       <c r="J5" s="1">
         <v>1.79</v>
@@ -1215,10 +1215,10 @@
         <v>78</v>
       </c>
       <c r="H6" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I6" s="1">
-        <v>249.873</v>
+        <v>263.73</v>
       </c>
       <c r="J6" s="1">
         <v>1.8</v>
@@ -1259,10 +1259,10 @@
         <v>78</v>
       </c>
       <c r="H7" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I7" s="1">
-        <v>24.809</v>
+        <v>16.289</v>
       </c>
       <c r="J7" s="1">
         <v>0.66</v>
@@ -1303,10 +1303,10 @@
         <v>78</v>
       </c>
       <c r="H8" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I8" s="1">
-        <v>96.89700000000001</v>
+        <v>102.271</v>
       </c>
       <c r="J8" s="1">
         <v>1.8</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="H9" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I9" s="1">
-        <v>44.999</v>
+        <v>47.865</v>
       </c>
       <c r="J9" s="1">
         <v>1.55</v>
@@ -1391,10 +1391,10 @@
         <v>78</v>
       </c>
       <c r="H10" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I10" s="1">
-        <v>31.166</v>
+        <v>33.151</v>
       </c>
       <c r="J10" s="1">
         <v>1.55</v>
@@ -1435,10 +1435,10 @@
         <v>78</v>
       </c>
       <c r="H11" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I11" s="1">
-        <v>48.815</v>
+        <v>51.923</v>
       </c>
       <c r="J11" s="1">
         <v>1.55</v>
@@ -1479,10 +1479,10 @@
         <v>78</v>
       </c>
       <c r="H12" s="1">
-        <v>1.779</v>
+        <v>2.03</v>
       </c>
       <c r="I12" s="1">
-        <v>104.089</v>
+        <v>118.775</v>
       </c>
       <c r="J12" s="1">
         <v>2.06</v>
@@ -1523,10 +1523,10 @@
         <v>78</v>
       </c>
       <c r="H13" s="1">
-        <v>1.419</v>
+        <v>1.52</v>
       </c>
       <c r="I13" s="1">
-        <v>54.121</v>
+        <v>57.973</v>
       </c>
       <c r="J13" s="1">
         <v>1.55</v>
@@ -1567,10 +1567,10 @@
         <v>78</v>
       </c>
       <c r="H14" s="1">
-        <v>1.419</v>
+        <v>1.52</v>
       </c>
       <c r="I14" s="1">
-        <v>48.728</v>
+        <v>52.197</v>
       </c>
       <c r="J14" s="1">
         <v>1.55</v>
@@ -1611,10 +1611,10 @@
         <v>78</v>
       </c>
       <c r="H15" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I15" s="1">
-        <v>31.571</v>
+        <v>20.728</v>
       </c>
       <c r="J15" s="1">
         <v>0.66</v>
@@ -1655,10 +1655,10 @@
         <v>78</v>
       </c>
       <c r="H16" s="1">
-        <v>1.769</v>
+        <v>2.03</v>
       </c>
       <c r="I16" s="1">
-        <v>120.186</v>
+        <v>137.918</v>
       </c>
       <c r="J16" s="1">
         <v>2.06</v>
@@ -1699,10 +1699,10 @@
         <v>78</v>
       </c>
       <c r="H17" s="1">
-        <v>1.409</v>
+        <v>1.52</v>
       </c>
       <c r="I17" s="1">
-        <v>27.701</v>
+        <v>29.883</v>
       </c>
       <c r="J17" s="1">
         <v>1.55</v>
@@ -1743,10 +1743,10 @@
         <v>78</v>
       </c>
       <c r="H18" s="1">
-        <v>1.644</v>
+        <v>1.77</v>
       </c>
       <c r="I18" s="1">
-        <v>68.127</v>
+        <v>73.349</v>
       </c>
       <c r="J18" s="1">
         <v>1.8</v>
@@ -1787,10 +1787,10 @@
         <v>78</v>
       </c>
       <c r="H19" s="1">
-        <v>1.644</v>
+        <v>1.77</v>
       </c>
       <c r="I19" s="1">
-        <v>98.64</v>
+        <v>106.2</v>
       </c>
       <c r="J19" s="1">
         <v>1.8</v>
@@ -1831,10 +1831,10 @@
         <v>78</v>
       </c>
       <c r="H20" s="1">
-        <v>1.409</v>
+        <v>1.53</v>
       </c>
       <c r="I20" s="1">
-        <v>27.081</v>
+        <v>29.407</v>
       </c>
       <c r="J20" s="1">
         <v>1.56</v>
@@ -1875,10 +1875,10 @@
         <v>78</v>
       </c>
       <c r="H21" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I21" s="1">
-        <v>21.978</v>
+        <v>14.43</v>
       </c>
       <c r="J21" s="1">
         <v>0.66</v>
@@ -1919,10 +1919,10 @@
         <v>78</v>
       </c>
       <c r="H22" s="1">
-        <v>1.644</v>
+        <v>1.76</v>
       </c>
       <c r="I22" s="1">
-        <v>116.658</v>
+        <v>124.89</v>
       </c>
       <c r="J22" s="1">
         <v>1.79</v>
@@ -1963,10 +1963,10 @@
         <v>78</v>
       </c>
       <c r="H23" s="1">
-        <v>1.769</v>
+        <v>2.02</v>
       </c>
       <c r="I23" s="1">
-        <v>118.222</v>
+        <v>134.997</v>
       </c>
       <c r="J23" s="1">
         <v>2.05</v>
@@ -2007,10 +2007,10 @@
         <v>78</v>
       </c>
       <c r="H24" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I24" s="1">
-        <v>65.601</v>
+        <v>70.074</v>
       </c>
       <c r="J24" s="1">
         <v>1.8</v>
@@ -2051,10 +2051,10 @@
         <v>78</v>
       </c>
       <c r="H25" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I25" s="1">
-        <v>50.872</v>
+        <v>54.468</v>
       </c>
       <c r="J25" s="1">
         <v>1.56</v>
@@ -2095,10 +2095,10 @@
         <v>78</v>
       </c>
       <c r="H26" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I26" s="1">
-        <v>64.791</v>
+        <v>69.37</v>
       </c>
       <c r="J26" s="1">
         <v>1.56</v>
@@ -2139,10 +2139,10 @@
         <v>78</v>
       </c>
       <c r="H27" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I27" s="1">
-        <v>59.634</v>
+        <v>62.941</v>
       </c>
       <c r="J27" s="1">
         <v>1.8</v>
@@ -2183,10 +2183,10 @@
         <v>78</v>
       </c>
       <c r="H28" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I28" s="1">
-        <v>41.255</v>
+        <v>44.171</v>
       </c>
       <c r="J28" s="1">
         <v>1.56</v>
@@ -2227,10 +2227,10 @@
         <v>78</v>
       </c>
       <c r="H29" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I29" s="1">
-        <v>253.227</v>
+        <v>270.29</v>
       </c>
       <c r="J29" s="1">
         <v>1.82</v>
@@ -2271,10 +2271,10 @@
         <v>78</v>
       </c>
       <c r="H30" s="1">
-        <v>1.779</v>
+        <v>2.05</v>
       </c>
       <c r="I30" s="1">
-        <v>104.427</v>
+        <v>120.335</v>
       </c>
       <c r="J30" s="1">
         <v>2.08</v>
@@ -2315,10 +2315,10 @@
         <v>78</v>
       </c>
       <c r="H31" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I31" s="1">
-        <v>32.007</v>
+        <v>21.014</v>
       </c>
       <c r="J31" s="1">
         <v>0.66</v>
@@ -2359,10 +2359,10 @@
         <v>78</v>
       </c>
       <c r="H32" s="1">
-        <v>1.799</v>
+        <v>2.07</v>
       </c>
       <c r="I32" s="1">
-        <v>34.091</v>
+        <v>39.226</v>
       </c>
       <c r="J32" s="1">
         <v>2.1</v>
@@ -2403,10 +2403,10 @@
         <v>78</v>
       </c>
       <c r="H33" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I33" s="1">
-        <v>36.475</v>
+        <v>38.75</v>
       </c>
       <c r="J33" s="1">
         <v>1.58</v>
@@ -2447,10 +2447,10 @@
         <v>78</v>
       </c>
       <c r="H34" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I34" s="1">
-        <v>103.14</v>
+        <v>109.2</v>
       </c>
       <c r="J34" s="1">
         <v>1.85</v>
@@ -2491,10 +2491,10 @@
         <v>78</v>
       </c>
       <c r="H35" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I35" s="1">
-        <v>300.825</v>
+        <v>318.5</v>
       </c>
       <c r="J35" s="1">
         <v>1.85</v>
@@ -2535,10 +2535,10 @@
         <v>78</v>
       </c>
       <c r="H36" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I36" s="1">
-        <v>109.242</v>
+        <v>115.661</v>
       </c>
       <c r="J36" s="1">
         <v>1.85</v>
@@ -2579,10 +2579,10 @@
         <v>78</v>
       </c>
       <c r="H37" s="1">
-        <v>1.819</v>
+        <v>2.08</v>
       </c>
       <c r="I37" s="1">
-        <v>104.32</v>
+        <v>119.288</v>
       </c>
       <c r="J37" s="1">
         <v>2.11</v>
@@ -2623,10 +2623,10 @@
         <v>78</v>
       </c>
       <c r="H38" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I38" s="1">
-        <v>32.536</v>
+        <v>34.565</v>
       </c>
       <c r="J38" s="1">
         <v>1.58</v>
@@ -2667,10 +2667,10 @@
         <v>78</v>
       </c>
       <c r="H39" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I39" s="1">
-        <v>49.197</v>
+        <v>52.603</v>
       </c>
       <c r="J39" s="1">
         <v>1.59</v>
@@ -2711,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="H40" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I40" s="1">
-        <v>36.256</v>
+        <v>38.766</v>
       </c>
       <c r="J40" s="1">
         <v>1.59</v>
@@ -2755,10 +2755,10 @@
         <v>78</v>
       </c>
       <c r="H41" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I41" s="1">
-        <v>35.878</v>
+        <v>23.556</v>
       </c>
       <c r="J41" s="1">
         <v>0.66</v>
@@ -2799,10 +2799,10 @@
         <v>78</v>
       </c>
       <c r="H42" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I42" s="1">
-        <v>111.752</v>
+        <v>118.318</v>
       </c>
       <c r="J42" s="1">
         <v>1.85</v>
@@ -2843,10 +2843,10 @@
         <v>78</v>
       </c>
       <c r="H43" s="1">
-        <v>1.819</v>
+        <v>2.07</v>
       </c>
       <c r="I43" s="1">
-        <v>107.157</v>
+        <v>121.944</v>
       </c>
       <c r="J43" s="1">
         <v>2.1</v>
@@ -2887,10 +2887,10 @@
         <v>78</v>
       </c>
       <c r="H44" s="1">
-        <v>1.459</v>
+        <v>1.57</v>
       </c>
       <c r="I44" s="1">
-        <v>69.974</v>
+        <v>75.297</v>
       </c>
       <c r="J44" s="1">
         <v>1.6</v>
@@ -2931,10 +2931,10 @@
         <v>78</v>
       </c>
       <c r="H45" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I45" s="1">
-        <v>35.224</v>
+        <v>23.127</v>
       </c>
       <c r="J45" s="1">
         <v>0.66</v>
@@ -2975,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="H46" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I46" s="1">
-        <v>223.453</v>
+        <v>235.282</v>
       </c>
       <c r="J46" s="1">
         <v>1.84</v>
@@ -3019,10 +3019,10 @@
         <v>78</v>
       </c>
       <c r="H47" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I47" s="1">
-        <v>39.874</v>
+        <v>43.181</v>
       </c>
       <c r="J47" s="1">
         <v>1.61</v>
@@ -3063,10 +3063,10 @@
         <v>78</v>
       </c>
       <c r="H48" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I48" s="1">
-        <v>57.426</v>
+        <v>62.189</v>
       </c>
       <c r="J48" s="1">
         <v>1.61</v>
@@ -3125,10 +3125,10 @@
         <v>15</v>
       </c>
       <c r="D53" s="8">
-        <v>1.68782</v>
+        <v>1.78997</v>
       </c>
       <c r="E53" s="6">
-        <v>2065.86</v>
+        <v>2190.88</v>
       </c>
       <c r="F53" s="6">
         <v>2227.6</v>
@@ -3145,10 +3145,10 @@
         <v>18</v>
       </c>
       <c r="D54" s="8">
-        <v>1.43829</v>
+        <v>1.54081</v>
       </c>
       <c r="E54" s="6">
-        <v>791.28</v>
+        <v>847.6799999999999</v>
       </c>
       <c r="F54" s="6">
         <v>864.1799999999999</v>
@@ -3165,10 +3165,10 @@
         <v>8</v>
       </c>
       <c r="D55" s="8">
-        <v>1.7833</v>
+        <v>2.04347</v>
       </c>
       <c r="E55" s="6">
-        <v>786.99</v>
+        <v>901.8</v>
       </c>
       <c r="F55" s="6">
         <v>915.04</v>
@@ -3185,10 +3185,10 @@
         <v>6</v>
       </c>
       <c r="D56" s="8">
-        <v>0.99</v>
+        <v>0.64999</v>
       </c>
       <c r="E56" s="6">
-        <v>181.47</v>
+        <v>119.14</v>
       </c>
       <c r="F56" s="6">
         <v>120.98</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="10">
-        <v>3825.6</v>
+        <v>4059.5</v>
       </c>
       <c r="F57" s="10">
         <v>4127.8</v>
